--- a/config/data_excel/WorkSpace_Driven_Customer.xlsx
+++ b/config/data_excel/WorkSpace_Driven_Customer.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+  <si>
+    <t>Test_Type</t>
+  </si>
   <si>
     <t>Search_Customer</t>
   </si>
@@ -133,7 +136,10 @@
     <t>edit_detaillokasi</t>
   </si>
   <si>
-    <t>Sinergi</t>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>Testing</t>
   </si>
   <si>
     <t>0895365597392</t>
@@ -235,6 +241,12 @@
     <t>Bandiung, Jawa Barat</t>
   </si>
   <si>
+    <t>NEGATIVE</t>
+  </si>
+  <si>
+    <t>Sinergi</t>
+  </si>
+  <si>
     <t>Tanggal Kontrak</t>
   </si>
   <si>
@@ -300,17 +312,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -539,7 +554,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="40" width="22.33"/>
+    <col customWidth="1" min="1" max="41" width="22.33"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
@@ -549,10 +564,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -663,135 +678,145 @@
       <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="5">
+      <c r="C2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="6">
         <v>46181.0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="3">
+      <c r="J2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="3">
         <v>2024.0</v>
       </c>
-      <c r="L2" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="Q2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="R2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="S2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="W2" s="3">
+      <c r="U2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="3">
         <v>15.0</v>
       </c>
-      <c r="X2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Y2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="Z2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AC2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AE2" s="3">
+      <c r="AD2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF2" s="3">
         <v>2021.0</v>
       </c>
-      <c r="AF2" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH2" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AG2" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AH2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AK2" s="9" t="s">
+      <c r="AI2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AK2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AL2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AM2" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="AN2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="5">
+      <c r="D3" s="3"/>
+      <c r="E3" s="6">
         <v>46198.0</v>
       </c>
-      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -807,16 +832,16 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="3" t="s">
-        <v>74</v>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3" t="s">
+        <v>78</v>
       </c>
-      <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="s">
-        <v>75</v>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3" t="s">
+        <v>79</v>
       </c>
-      <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
@@ -831,12 +856,13 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -873,13 +899,14 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -915,6 +942,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
+      <c r="AO5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
@@ -957,6 +985,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
@@ -999,6 +1028,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
@@ -1041,6 +1071,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
@@ -1083,6 +1114,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
@@ -1125,6 +1157,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3"/>
@@ -1167,6 +1200,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3"/>
@@ -1209,6 +1243,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
@@ -1251,6 +1286,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3"/>
@@ -1293,6 +1329,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3"/>
@@ -1335,6 +1372,7 @@
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
@@ -1377,6 +1415,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
@@ -1419,6 +1458,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
@@ -1461,6 +1501,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
@@ -1503,6 +1544,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
@@ -1545,6 +1587,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
@@ -1587,6 +1630,7 @@
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
@@ -1629,6 +1673,7 @@
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
@@ -1671,6 +1716,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
@@ -1713,6 +1759,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
@@ -1755,6 +1802,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
@@ -1797,6 +1845,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
@@ -1839,6 +1888,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
+      <c r="AO27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
@@ -1881,6 +1931,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
@@ -1923,6 +1974,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
@@ -1965,6 +2017,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
+      <c r="AO30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
@@ -2007,6 +2060,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
+      <c r="AO31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
@@ -2049,6 +2103,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
       <c r="AN32" s="3"/>
+      <c r="AO32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
@@ -2091,6 +2146,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
+      <c r="AO33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
@@ -2133,6 +2189,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
+      <c r="AO34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
@@ -2175,6 +2232,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
+      <c r="AO35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
@@ -2217,6 +2275,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
+      <c r="AO36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
@@ -2259,6 +2318,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
+      <c r="AO37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
@@ -2301,6 +2361,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
+      <c r="AO38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
@@ -2343,6 +2404,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
@@ -2385,6 +2447,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
@@ -2427,6 +2490,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
+      <c r="AO41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
@@ -2469,6 +2533,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
+      <c r="AO42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
@@ -2511,6 +2576,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
+      <c r="AO43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
@@ -2553,6 +2619,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
+      <c r="AO44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
@@ -2595,6 +2662,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
+      <c r="AO45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
@@ -2637,6 +2705,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
+      <c r="AO46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
@@ -2679,6 +2748,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
+      <c r="AO47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
@@ -2721,6 +2791,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
+      <c r="AO48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
@@ -2763,6 +2834,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
+      <c r="AO49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
@@ -2805,6 +2877,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
+      <c r="AO50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
@@ -2847,6 +2920,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
       <c r="AN51" s="3"/>
+      <c r="AO51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
@@ -2889,6 +2963,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
       <c r="AN52" s="3"/>
+      <c r="AO52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
@@ -2931,6 +3006,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
       <c r="AN53" s="3"/>
+      <c r="AO53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
@@ -2973,6 +3049,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
       <c r="AN54" s="3"/>
+      <c r="AO54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
@@ -3015,6 +3092,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
@@ -3057,6 +3135,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
@@ -3099,6 +3178,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
       <c r="AN57" s="3"/>
+      <c r="AO57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
@@ -3141,6 +3221,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
       <c r="AN58" s="3"/>
+      <c r="AO58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
@@ -3183,6 +3264,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
       <c r="AN59" s="3"/>
+      <c r="AO59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
@@ -3225,6 +3307,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
       <c r="AN60" s="3"/>
+      <c r="AO60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
@@ -3267,6 +3350,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
       <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
@@ -3309,6 +3393,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
       <c r="AN62" s="3"/>
+      <c r="AO62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
@@ -3351,6 +3436,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
       <c r="AN63" s="3"/>
+      <c r="AO63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
@@ -3393,6 +3479,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
       <c r="AN64" s="3"/>
+      <c r="AO64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
@@ -3435,6 +3522,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
       <c r="AN65" s="3"/>
+      <c r="AO65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
@@ -3477,6 +3565,7 @@
       <c r="AL66" s="3"/>
       <c r="AM66" s="3"/>
       <c r="AN66" s="3"/>
+      <c r="AO66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
@@ -3519,6 +3608,7 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
@@ -3561,6 +3651,7 @@
       <c r="AL68" s="3"/>
       <c r="AM68" s="3"/>
       <c r="AN68" s="3"/>
+      <c r="AO68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
@@ -3603,6 +3694,7 @@
       <c r="AL69" s="3"/>
       <c r="AM69" s="3"/>
       <c r="AN69" s="3"/>
+      <c r="AO69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
@@ -3645,6 +3737,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
       <c r="AN70" s="3"/>
+      <c r="AO70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
@@ -3687,6 +3780,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
       <c r="AN71" s="3"/>
+      <c r="AO71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
@@ -3729,6 +3823,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
       <c r="AN72" s="3"/>
+      <c r="AO72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
@@ -3771,6 +3866,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
       <c r="AN73" s="3"/>
+      <c r="AO73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
@@ -3813,6 +3909,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
       <c r="AN74" s="3"/>
+      <c r="AO74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
@@ -3855,6 +3952,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
       <c r="AN75" s="3"/>
+      <c r="AO75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
@@ -3897,6 +3995,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
       <c r="AN76" s="3"/>
+      <c r="AO76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
@@ -3939,6 +4038,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
       <c r="AN77" s="3"/>
+      <c r="AO77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
@@ -3981,6 +4081,7 @@
       <c r="AL78" s="3"/>
       <c r="AM78" s="3"/>
       <c r="AN78" s="3"/>
+      <c r="AO78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
@@ -4023,6 +4124,7 @@
       <c r="AL79" s="3"/>
       <c r="AM79" s="3"/>
       <c r="AN79" s="3"/>
+      <c r="AO79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
@@ -4065,6 +4167,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
       <c r="AN80" s="3"/>
+      <c r="AO80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
@@ -4107,6 +4210,7 @@
       <c r="AL81" s="3"/>
       <c r="AM81" s="3"/>
       <c r="AN81" s="3"/>
+      <c r="AO81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
@@ -4149,6 +4253,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
@@ -4191,6 +4296,7 @@
       <c r="AL83" s="3"/>
       <c r="AM83" s="3"/>
       <c r="AN83" s="3"/>
+      <c r="AO83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
@@ -4233,6 +4339,7 @@
       <c r="AL84" s="3"/>
       <c r="AM84" s="3"/>
       <c r="AN84" s="3"/>
+      <c r="AO84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
@@ -4275,6 +4382,7 @@
       <c r="AL85" s="3"/>
       <c r="AM85" s="3"/>
       <c r="AN85" s="3"/>
+      <c r="AO85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
@@ -4317,6 +4425,7 @@
       <c r="AL86" s="3"/>
       <c r="AM86" s="3"/>
       <c r="AN86" s="3"/>
+      <c r="AO86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
@@ -4359,6 +4468,7 @@
       <c r="AL87" s="3"/>
       <c r="AM87" s="3"/>
       <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
@@ -4401,6 +4511,7 @@
       <c r="AL88" s="3"/>
       <c r="AM88" s="3"/>
       <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
@@ -4443,6 +4554,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
       <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
@@ -4485,6 +4597,7 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
@@ -4527,6 +4640,7 @@
       <c r="AL91" s="3"/>
       <c r="AM91" s="3"/>
       <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
@@ -4569,6 +4683,7 @@
       <c r="AL92" s="3"/>
       <c r="AM92" s="3"/>
       <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
@@ -4611,6 +4726,7 @@
       <c r="AL93" s="3"/>
       <c r="AM93" s="3"/>
       <c r="AN93" s="3"/>
+      <c r="AO93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
@@ -4653,6 +4769,7 @@
       <c r="AL94" s="3"/>
       <c r="AM94" s="3"/>
       <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
@@ -4695,6 +4812,7 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
@@ -4737,6 +4855,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
       <c r="AN96" s="3"/>
+      <c r="AO96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
@@ -4779,6 +4898,7 @@
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
       <c r="AN97" s="3"/>
+      <c r="AO97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
@@ -4821,6 +4941,7 @@
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
       <c r="AN98" s="3"/>
+      <c r="AO98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
@@ -4863,6 +4984,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
       <c r="AN99" s="3"/>
+      <c r="AO99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
@@ -4905,6 +5027,7 @@
       <c r="AL100" s="3"/>
       <c r="AM100" s="3"/>
       <c r="AN100" s="3"/>
+      <c r="AO100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
@@ -4947,6 +5070,7 @@
       <c r="AL101" s="3"/>
       <c r="AM101" s="3"/>
       <c r="AN101" s="3"/>
+      <c r="AO101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
@@ -4989,6 +5113,7 @@
       <c r="AL102" s="3"/>
       <c r="AM102" s="3"/>
       <c r="AN102" s="3"/>
+      <c r="AO102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
@@ -5031,6 +5156,7 @@
       <c r="AL103" s="3"/>
       <c r="AM103" s="3"/>
       <c r="AN103" s="3"/>
+      <c r="AO103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
@@ -5073,6 +5199,7 @@
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
       <c r="AN104" s="3"/>
+      <c r="AO104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
@@ -5115,6 +5242,7 @@
       <c r="AL105" s="3"/>
       <c r="AM105" s="3"/>
       <c r="AN105" s="3"/>
+      <c r="AO105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
@@ -5157,6 +5285,7 @@
       <c r="AL106" s="3"/>
       <c r="AM106" s="3"/>
       <c r="AN106" s="3"/>
+      <c r="AO106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
@@ -5199,6 +5328,7 @@
       <c r="AL107" s="3"/>
       <c r="AM107" s="3"/>
       <c r="AN107" s="3"/>
+      <c r="AO107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
@@ -5241,6 +5371,7 @@
       <c r="AL108" s="3"/>
       <c r="AM108" s="3"/>
       <c r="AN108" s="3"/>
+      <c r="AO108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
@@ -5283,6 +5414,7 @@
       <c r="AL109" s="3"/>
       <c r="AM109" s="3"/>
       <c r="AN109" s="3"/>
+      <c r="AO109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
@@ -5325,6 +5457,7 @@
       <c r="AL110" s="3"/>
       <c r="AM110" s="3"/>
       <c r="AN110" s="3"/>
+      <c r="AO110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
@@ -5367,6 +5500,7 @@
       <c r="AL111" s="3"/>
       <c r="AM111" s="3"/>
       <c r="AN111" s="3"/>
+      <c r="AO111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
@@ -5409,6 +5543,7 @@
       <c r="AL112" s="3"/>
       <c r="AM112" s="3"/>
       <c r="AN112" s="3"/>
+      <c r="AO112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
@@ -5451,6 +5586,7 @@
       <c r="AL113" s="3"/>
       <c r="AM113" s="3"/>
       <c r="AN113" s="3"/>
+      <c r="AO113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
@@ -5493,6 +5629,7 @@
       <c r="AL114" s="3"/>
       <c r="AM114" s="3"/>
       <c r="AN114" s="3"/>
+      <c r="AO114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
@@ -5535,6 +5672,7 @@
       <c r="AL115" s="3"/>
       <c r="AM115" s="3"/>
       <c r="AN115" s="3"/>
+      <c r="AO115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
@@ -5577,6 +5715,7 @@
       <c r="AL116" s="3"/>
       <c r="AM116" s="3"/>
       <c r="AN116" s="3"/>
+      <c r="AO116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
@@ -5619,6 +5758,7 @@
       <c r="AL117" s="3"/>
       <c r="AM117" s="3"/>
       <c r="AN117" s="3"/>
+      <c r="AO117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
@@ -5661,6 +5801,7 @@
       <c r="AL118" s="3"/>
       <c r="AM118" s="3"/>
       <c r="AN118" s="3"/>
+      <c r="AO118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
@@ -5703,6 +5844,7 @@
       <c r="AL119" s="3"/>
       <c r="AM119" s="3"/>
       <c r="AN119" s="3"/>
+      <c r="AO119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
@@ -5745,6 +5887,7 @@
       <c r="AL120" s="3"/>
       <c r="AM120" s="3"/>
       <c r="AN120" s="3"/>
+      <c r="AO120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
@@ -5787,6 +5930,7 @@
       <c r="AL121" s="3"/>
       <c r="AM121" s="3"/>
       <c r="AN121" s="3"/>
+      <c r="AO121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
@@ -5829,6 +5973,7 @@
       <c r="AL122" s="3"/>
       <c r="AM122" s="3"/>
       <c r="AN122" s="3"/>
+      <c r="AO122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
@@ -5871,6 +6016,7 @@
       <c r="AL123" s="3"/>
       <c r="AM123" s="3"/>
       <c r="AN123" s="3"/>
+      <c r="AO123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
@@ -5913,6 +6059,7 @@
       <c r="AL124" s="3"/>
       <c r="AM124" s="3"/>
       <c r="AN124" s="3"/>
+      <c r="AO124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
@@ -5955,6 +6102,7 @@
       <c r="AL125" s="3"/>
       <c r="AM125" s="3"/>
       <c r="AN125" s="3"/>
+      <c r="AO125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
@@ -5997,6 +6145,7 @@
       <c r="AL126" s="3"/>
       <c r="AM126" s="3"/>
       <c r="AN126" s="3"/>
+      <c r="AO126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
@@ -6039,6 +6188,7 @@
       <c r="AL127" s="3"/>
       <c r="AM127" s="3"/>
       <c r="AN127" s="3"/>
+      <c r="AO127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
@@ -6081,6 +6231,7 @@
       <c r="AL128" s="3"/>
       <c r="AM128" s="3"/>
       <c r="AN128" s="3"/>
+      <c r="AO128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
@@ -6123,6 +6274,7 @@
       <c r="AL129" s="3"/>
       <c r="AM129" s="3"/>
       <c r="AN129" s="3"/>
+      <c r="AO129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
@@ -6165,6 +6317,7 @@
       <c r="AL130" s="3"/>
       <c r="AM130" s="3"/>
       <c r="AN130" s="3"/>
+      <c r="AO130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
@@ -6207,6 +6360,7 @@
       <c r="AL131" s="3"/>
       <c r="AM131" s="3"/>
       <c r="AN131" s="3"/>
+      <c r="AO131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
@@ -6249,6 +6403,7 @@
       <c r="AL132" s="3"/>
       <c r="AM132" s="3"/>
       <c r="AN132" s="3"/>
+      <c r="AO132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
@@ -6291,6 +6446,7 @@
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
       <c r="AN133" s="3"/>
+      <c r="AO133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
@@ -6333,6 +6489,7 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
       <c r="AN134" s="3"/>
+      <c r="AO134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
@@ -6375,6 +6532,7 @@
       <c r="AL135" s="3"/>
       <c r="AM135" s="3"/>
       <c r="AN135" s="3"/>
+      <c r="AO135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
@@ -6417,6 +6575,7 @@
       <c r="AL136" s="3"/>
       <c r="AM136" s="3"/>
       <c r="AN136" s="3"/>
+      <c r="AO136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
@@ -6459,6 +6618,7 @@
       <c r="AL137" s="3"/>
       <c r="AM137" s="3"/>
       <c r="AN137" s="3"/>
+      <c r="AO137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
@@ -6501,6 +6661,7 @@
       <c r="AL138" s="3"/>
       <c r="AM138" s="3"/>
       <c r="AN138" s="3"/>
+      <c r="AO138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
@@ -6543,6 +6704,7 @@
       <c r="AL139" s="3"/>
       <c r="AM139" s="3"/>
       <c r="AN139" s="3"/>
+      <c r="AO139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
@@ -6585,6 +6747,7 @@
       <c r="AL140" s="3"/>
       <c r="AM140" s="3"/>
       <c r="AN140" s="3"/>
+      <c r="AO140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
@@ -6627,6 +6790,7 @@
       <c r="AL141" s="3"/>
       <c r="AM141" s="3"/>
       <c r="AN141" s="3"/>
+      <c r="AO141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
@@ -6669,6 +6833,7 @@
       <c r="AL142" s="3"/>
       <c r="AM142" s="3"/>
       <c r="AN142" s="3"/>
+      <c r="AO142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
@@ -6711,6 +6876,7 @@
       <c r="AL143" s="3"/>
       <c r="AM143" s="3"/>
       <c r="AN143" s="3"/>
+      <c r="AO143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
@@ -6753,6 +6919,7 @@
       <c r="AL144" s="3"/>
       <c r="AM144" s="3"/>
       <c r="AN144" s="3"/>
+      <c r="AO144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
@@ -6795,6 +6962,7 @@
       <c r="AL145" s="3"/>
       <c r="AM145" s="3"/>
       <c r="AN145" s="3"/>
+      <c r="AO145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
@@ -6837,6 +7005,7 @@
       <c r="AL146" s="3"/>
       <c r="AM146" s="3"/>
       <c r="AN146" s="3"/>
+      <c r="AO146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
@@ -6879,6 +7048,7 @@
       <c r="AL147" s="3"/>
       <c r="AM147" s="3"/>
       <c r="AN147" s="3"/>
+      <c r="AO147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
@@ -6921,6 +7091,7 @@
       <c r="AL148" s="3"/>
       <c r="AM148" s="3"/>
       <c r="AN148" s="3"/>
+      <c r="AO148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
@@ -6963,6 +7134,7 @@
       <c r="AL149" s="3"/>
       <c r="AM149" s="3"/>
       <c r="AN149" s="3"/>
+      <c r="AO149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
@@ -7005,6 +7177,7 @@
       <c r="AL150" s="3"/>
       <c r="AM150" s="3"/>
       <c r="AN150" s="3"/>
+      <c r="AO150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
@@ -7047,6 +7220,7 @@
       <c r="AL151" s="3"/>
       <c r="AM151" s="3"/>
       <c r="AN151" s="3"/>
+      <c r="AO151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
@@ -7089,6 +7263,7 @@
       <c r="AL152" s="3"/>
       <c r="AM152" s="3"/>
       <c r="AN152" s="3"/>
+      <c r="AO152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
@@ -7131,6 +7306,7 @@
       <c r="AL153" s="3"/>
       <c r="AM153" s="3"/>
       <c r="AN153" s="3"/>
+      <c r="AO153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
@@ -7173,6 +7349,7 @@
       <c r="AL154" s="3"/>
       <c r="AM154" s="3"/>
       <c r="AN154" s="3"/>
+      <c r="AO154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
@@ -7215,6 +7392,7 @@
       <c r="AL155" s="3"/>
       <c r="AM155" s="3"/>
       <c r="AN155" s="3"/>
+      <c r="AO155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
@@ -7257,6 +7435,7 @@
       <c r="AL156" s="3"/>
       <c r="AM156" s="3"/>
       <c r="AN156" s="3"/>
+      <c r="AO156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
@@ -7299,6 +7478,7 @@
       <c r="AL157" s="3"/>
       <c r="AM157" s="3"/>
       <c r="AN157" s="3"/>
+      <c r="AO157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
@@ -7341,6 +7521,7 @@
       <c r="AL158" s="3"/>
       <c r="AM158" s="3"/>
       <c r="AN158" s="3"/>
+      <c r="AO158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
@@ -7383,6 +7564,7 @@
       <c r="AL159" s="3"/>
       <c r="AM159" s="3"/>
       <c r="AN159" s="3"/>
+      <c r="AO159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
@@ -7425,6 +7607,7 @@
       <c r="AL160" s="3"/>
       <c r="AM160" s="3"/>
       <c r="AN160" s="3"/>
+      <c r="AO160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
@@ -7467,6 +7650,7 @@
       <c r="AL161" s="3"/>
       <c r="AM161" s="3"/>
       <c r="AN161" s="3"/>
+      <c r="AO161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
@@ -7509,6 +7693,7 @@
       <c r="AL162" s="3"/>
       <c r="AM162" s="3"/>
       <c r="AN162" s="3"/>
+      <c r="AO162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
@@ -7551,6 +7736,7 @@
       <c r="AL163" s="3"/>
       <c r="AM163" s="3"/>
       <c r="AN163" s="3"/>
+      <c r="AO163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
@@ -7593,6 +7779,7 @@
       <c r="AL164" s="3"/>
       <c r="AM164" s="3"/>
       <c r="AN164" s="3"/>
+      <c r="AO164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
@@ -7635,6 +7822,7 @@
       <c r="AL165" s="3"/>
       <c r="AM165" s="3"/>
       <c r="AN165" s="3"/>
+      <c r="AO165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
@@ -7677,6 +7865,7 @@
       <c r="AL166" s="3"/>
       <c r="AM166" s="3"/>
       <c r="AN166" s="3"/>
+      <c r="AO166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
@@ -7719,6 +7908,7 @@
       <c r="AL167" s="3"/>
       <c r="AM167" s="3"/>
       <c r="AN167" s="3"/>
+      <c r="AO167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
@@ -7761,6 +7951,7 @@
       <c r="AL168" s="3"/>
       <c r="AM168" s="3"/>
       <c r="AN168" s="3"/>
+      <c r="AO168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
@@ -7803,6 +7994,7 @@
       <c r="AL169" s="3"/>
       <c r="AM169" s="3"/>
       <c r="AN169" s="3"/>
+      <c r="AO169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
@@ -7845,6 +8037,7 @@
       <c r="AL170" s="3"/>
       <c r="AM170" s="3"/>
       <c r="AN170" s="3"/>
+      <c r="AO170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
@@ -7887,6 +8080,7 @@
       <c r="AL171" s="3"/>
       <c r="AM171" s="3"/>
       <c r="AN171" s="3"/>
+      <c r="AO171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
@@ -7929,6 +8123,7 @@
       <c r="AL172" s="3"/>
       <c r="AM172" s="3"/>
       <c r="AN172" s="3"/>
+      <c r="AO172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
@@ -7971,6 +8166,7 @@
       <c r="AL173" s="3"/>
       <c r="AM173" s="3"/>
       <c r="AN173" s="3"/>
+      <c r="AO173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
@@ -8013,6 +8209,7 @@
       <c r="AL174" s="3"/>
       <c r="AM174" s="3"/>
       <c r="AN174" s="3"/>
+      <c r="AO174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
@@ -8055,6 +8252,7 @@
       <c r="AL175" s="3"/>
       <c r="AM175" s="3"/>
       <c r="AN175" s="3"/>
+      <c r="AO175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
@@ -8097,6 +8295,7 @@
       <c r="AL176" s="3"/>
       <c r="AM176" s="3"/>
       <c r="AN176" s="3"/>
+      <c r="AO176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
@@ -8139,6 +8338,7 @@
       <c r="AL177" s="3"/>
       <c r="AM177" s="3"/>
       <c r="AN177" s="3"/>
+      <c r="AO177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
@@ -8181,6 +8381,7 @@
       <c r="AL178" s="3"/>
       <c r="AM178" s="3"/>
       <c r="AN178" s="3"/>
+      <c r="AO178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
@@ -8223,6 +8424,7 @@
       <c r="AL179" s="3"/>
       <c r="AM179" s="3"/>
       <c r="AN179" s="3"/>
+      <c r="AO179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
@@ -8265,6 +8467,7 @@
       <c r="AL180" s="3"/>
       <c r="AM180" s="3"/>
       <c r="AN180" s="3"/>
+      <c r="AO180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
@@ -8307,6 +8510,7 @@
       <c r="AL181" s="3"/>
       <c r="AM181" s="3"/>
       <c r="AN181" s="3"/>
+      <c r="AO181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
@@ -8349,6 +8553,7 @@
       <c r="AL182" s="3"/>
       <c r="AM182" s="3"/>
       <c r="AN182" s="3"/>
+      <c r="AO182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
@@ -8391,6 +8596,7 @@
       <c r="AL183" s="3"/>
       <c r="AM183" s="3"/>
       <c r="AN183" s="3"/>
+      <c r="AO183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
@@ -8433,6 +8639,7 @@
       <c r="AL184" s="3"/>
       <c r="AM184" s="3"/>
       <c r="AN184" s="3"/>
+      <c r="AO184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
@@ -8475,6 +8682,7 @@
       <c r="AL185" s="3"/>
       <c r="AM185" s="3"/>
       <c r="AN185" s="3"/>
+      <c r="AO185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
@@ -8517,6 +8725,7 @@
       <c r="AL186" s="3"/>
       <c r="AM186" s="3"/>
       <c r="AN186" s="3"/>
+      <c r="AO186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
@@ -8559,6 +8768,7 @@
       <c r="AL187" s="3"/>
       <c r="AM187" s="3"/>
       <c r="AN187" s="3"/>
+      <c r="AO187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
@@ -8601,6 +8811,7 @@
       <c r="AL188" s="3"/>
       <c r="AM188" s="3"/>
       <c r="AN188" s="3"/>
+      <c r="AO188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
@@ -8643,6 +8854,7 @@
       <c r="AL189" s="3"/>
       <c r="AM189" s="3"/>
       <c r="AN189" s="3"/>
+      <c r="AO189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
@@ -8685,6 +8897,7 @@
       <c r="AL190" s="3"/>
       <c r="AM190" s="3"/>
       <c r="AN190" s="3"/>
+      <c r="AO190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
@@ -8727,6 +8940,7 @@
       <c r="AL191" s="3"/>
       <c r="AM191" s="3"/>
       <c r="AN191" s="3"/>
+      <c r="AO191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
@@ -8769,6 +8983,7 @@
       <c r="AL192" s="3"/>
       <c r="AM192" s="3"/>
       <c r="AN192" s="3"/>
+      <c r="AO192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
@@ -8811,6 +9026,7 @@
       <c r="AL193" s="3"/>
       <c r="AM193" s="3"/>
       <c r="AN193" s="3"/>
+      <c r="AO193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
@@ -8853,6 +9069,7 @@
       <c r="AL194" s="3"/>
       <c r="AM194" s="3"/>
       <c r="AN194" s="3"/>
+      <c r="AO194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
@@ -8895,6 +9112,7 @@
       <c r="AL195" s="3"/>
       <c r="AM195" s="3"/>
       <c r="AN195" s="3"/>
+      <c r="AO195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
@@ -8937,6 +9155,7 @@
       <c r="AL196" s="3"/>
       <c r="AM196" s="3"/>
       <c r="AN196" s="3"/>
+      <c r="AO196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
@@ -8979,6 +9198,7 @@
       <c r="AL197" s="3"/>
       <c r="AM197" s="3"/>
       <c r="AN197" s="3"/>
+      <c r="AO197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
@@ -9021,6 +9241,7 @@
       <c r="AL198" s="3"/>
       <c r="AM198" s="3"/>
       <c r="AN198" s="3"/>
+      <c r="AO198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
@@ -9063,6 +9284,7 @@
       <c r="AL199" s="3"/>
       <c r="AM199" s="3"/>
       <c r="AN199" s="3"/>
+      <c r="AO199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
@@ -9105,6 +9327,7 @@
       <c r="AL200" s="3"/>
       <c r="AM200" s="3"/>
       <c r="AN200" s="3"/>
+      <c r="AO200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
@@ -9147,6 +9370,7 @@
       <c r="AL201" s="3"/>
       <c r="AM201" s="3"/>
       <c r="AN201" s="3"/>
+      <c r="AO201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
@@ -9189,6 +9413,7 @@
       <c r="AL202" s="3"/>
       <c r="AM202" s="3"/>
       <c r="AN202" s="3"/>
+      <c r="AO202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
@@ -9231,6 +9456,7 @@
       <c r="AL203" s="3"/>
       <c r="AM203" s="3"/>
       <c r="AN203" s="3"/>
+      <c r="AO203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
@@ -9273,6 +9499,7 @@
       <c r="AL204" s="3"/>
       <c r="AM204" s="3"/>
       <c r="AN204" s="3"/>
+      <c r="AO204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
@@ -9315,6 +9542,7 @@
       <c r="AL205" s="3"/>
       <c r="AM205" s="3"/>
       <c r="AN205" s="3"/>
+      <c r="AO205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
@@ -9357,6 +9585,7 @@
       <c r="AL206" s="3"/>
       <c r="AM206" s="3"/>
       <c r="AN206" s="3"/>
+      <c r="AO206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
@@ -9399,6 +9628,7 @@
       <c r="AL207" s="3"/>
       <c r="AM207" s="3"/>
       <c r="AN207" s="3"/>
+      <c r="AO207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
@@ -9441,6 +9671,7 @@
       <c r="AL208" s="3"/>
       <c r="AM208" s="3"/>
       <c r="AN208" s="3"/>
+      <c r="AO208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
@@ -9483,6 +9714,7 @@
       <c r="AL209" s="3"/>
       <c r="AM209" s="3"/>
       <c r="AN209" s="3"/>
+      <c r="AO209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
@@ -9525,6 +9757,7 @@
       <c r="AL210" s="3"/>
       <c r="AM210" s="3"/>
       <c r="AN210" s="3"/>
+      <c r="AO210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
@@ -9567,6 +9800,7 @@
       <c r="AL211" s="3"/>
       <c r="AM211" s="3"/>
       <c r="AN211" s="3"/>
+      <c r="AO211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
@@ -9609,6 +9843,7 @@
       <c r="AL212" s="3"/>
       <c r="AM212" s="3"/>
       <c r="AN212" s="3"/>
+      <c r="AO212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
@@ -9651,6 +9886,7 @@
       <c r="AL213" s="3"/>
       <c r="AM213" s="3"/>
       <c r="AN213" s="3"/>
+      <c r="AO213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
@@ -9693,6 +9929,7 @@
       <c r="AL214" s="3"/>
       <c r="AM214" s="3"/>
       <c r="AN214" s="3"/>
+      <c r="AO214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
@@ -9735,6 +9972,7 @@
       <c r="AL215" s="3"/>
       <c r="AM215" s="3"/>
       <c r="AN215" s="3"/>
+      <c r="AO215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
@@ -9777,6 +10015,7 @@
       <c r="AL216" s="3"/>
       <c r="AM216" s="3"/>
       <c r="AN216" s="3"/>
+      <c r="AO216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
@@ -9819,6 +10058,7 @@
       <c r="AL217" s="3"/>
       <c r="AM217" s="3"/>
       <c r="AN217" s="3"/>
+      <c r="AO217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
@@ -9861,6 +10101,7 @@
       <c r="AL218" s="3"/>
       <c r="AM218" s="3"/>
       <c r="AN218" s="3"/>
+      <c r="AO218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
@@ -9903,6 +10144,7 @@
       <c r="AL219" s="3"/>
       <c r="AM219" s="3"/>
       <c r="AN219" s="3"/>
+      <c r="AO219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
@@ -9945,6 +10187,7 @@
       <c r="AL220" s="3"/>
       <c r="AM220" s="3"/>
       <c r="AN220" s="3"/>
+      <c r="AO220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="3"/>
@@ -9987,6 +10230,7 @@
       <c r="AL221" s="3"/>
       <c r="AM221" s="3"/>
       <c r="AN221" s="3"/>
+      <c r="AO221" s="3"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="3"/>
@@ -10029,6 +10273,7 @@
       <c r="AL222" s="3"/>
       <c r="AM222" s="3"/>
       <c r="AN222" s="3"/>
+      <c r="AO222" s="3"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="3"/>
@@ -10071,6 +10316,7 @@
       <c r="AL223" s="3"/>
       <c r="AM223" s="3"/>
       <c r="AN223" s="3"/>
+      <c r="AO223" s="3"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="3"/>
@@ -10113,6 +10359,7 @@
       <c r="AL224" s="3"/>
       <c r="AM224" s="3"/>
       <c r="AN224" s="3"/>
+      <c r="AO224" s="3"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="3"/>
@@ -10155,6 +10402,7 @@
       <c r="AL225" s="3"/>
       <c r="AM225" s="3"/>
       <c r="AN225" s="3"/>
+      <c r="AO225" s="3"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="3"/>
@@ -10197,6 +10445,7 @@
       <c r="AL226" s="3"/>
       <c r="AM226" s="3"/>
       <c r="AN226" s="3"/>
+      <c r="AO226" s="3"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="3"/>
@@ -10239,6 +10488,7 @@
       <c r="AL227" s="3"/>
       <c r="AM227" s="3"/>
       <c r="AN227" s="3"/>
+      <c r="AO227" s="3"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="3"/>
@@ -10281,6 +10531,7 @@
       <c r="AL228" s="3"/>
       <c r="AM228" s="3"/>
       <c r="AN228" s="3"/>
+      <c r="AO228" s="3"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="3"/>
@@ -10323,6 +10574,7 @@
       <c r="AL229" s="3"/>
       <c r="AM229" s="3"/>
       <c r="AN229" s="3"/>
+      <c r="AO229" s="3"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="3"/>
@@ -10365,6 +10617,7 @@
       <c r="AL230" s="3"/>
       <c r="AM230" s="3"/>
       <c r="AN230" s="3"/>
+      <c r="AO230" s="3"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="3"/>
@@ -10407,6 +10660,7 @@
       <c r="AL231" s="3"/>
       <c r="AM231" s="3"/>
       <c r="AN231" s="3"/>
+      <c r="AO231" s="3"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="3"/>
@@ -10449,6 +10703,7 @@
       <c r="AL232" s="3"/>
       <c r="AM232" s="3"/>
       <c r="AN232" s="3"/>
+      <c r="AO232" s="3"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="3"/>
@@ -10491,6 +10746,7 @@
       <c r="AL233" s="3"/>
       <c r="AM233" s="3"/>
       <c r="AN233" s="3"/>
+      <c r="AO233" s="3"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="3"/>
@@ -10533,6 +10789,7 @@
       <c r="AL234" s="3"/>
       <c r="AM234" s="3"/>
       <c r="AN234" s="3"/>
+      <c r="AO234" s="3"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="3"/>
@@ -10575,6 +10832,7 @@
       <c r="AL235" s="3"/>
       <c r="AM235" s="3"/>
       <c r="AN235" s="3"/>
+      <c r="AO235" s="3"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="3"/>
@@ -10617,6 +10875,7 @@
       <c r="AL236" s="3"/>
       <c r="AM236" s="3"/>
       <c r="AN236" s="3"/>
+      <c r="AO236" s="3"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="3"/>
@@ -10659,6 +10918,7 @@
       <c r="AL237" s="3"/>
       <c r="AM237" s="3"/>
       <c r="AN237" s="3"/>
+      <c r="AO237" s="3"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="3"/>
@@ -10701,6 +10961,7 @@
       <c r="AL238" s="3"/>
       <c r="AM238" s="3"/>
       <c r="AN238" s="3"/>
+      <c r="AO238" s="3"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="3"/>
@@ -10743,6 +11004,7 @@
       <c r="AL239" s="3"/>
       <c r="AM239" s="3"/>
       <c r="AN239" s="3"/>
+      <c r="AO239" s="3"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="3"/>
@@ -10785,6 +11047,7 @@
       <c r="AL240" s="3"/>
       <c r="AM240" s="3"/>
       <c r="AN240" s="3"/>
+      <c r="AO240" s="3"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="3"/>
@@ -10827,6 +11090,7 @@
       <c r="AL241" s="3"/>
       <c r="AM241" s="3"/>
       <c r="AN241" s="3"/>
+      <c r="AO241" s="3"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="3"/>
@@ -10869,6 +11133,7 @@
       <c r="AL242" s="3"/>
       <c r="AM242" s="3"/>
       <c r="AN242" s="3"/>
+      <c r="AO242" s="3"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="3"/>
@@ -10911,6 +11176,7 @@
       <c r="AL243" s="3"/>
       <c r="AM243" s="3"/>
       <c r="AN243" s="3"/>
+      <c r="AO243" s="3"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="3"/>
@@ -10953,6 +11219,7 @@
       <c r="AL244" s="3"/>
       <c r="AM244" s="3"/>
       <c r="AN244" s="3"/>
+      <c r="AO244" s="3"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="3"/>
@@ -10995,6 +11262,7 @@
       <c r="AL245" s="3"/>
       <c r="AM245" s="3"/>
       <c r="AN245" s="3"/>
+      <c r="AO245" s="3"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="3"/>
@@ -11037,6 +11305,7 @@
       <c r="AL246" s="3"/>
       <c r="AM246" s="3"/>
       <c r="AN246" s="3"/>
+      <c r="AO246" s="3"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="3"/>
@@ -11079,6 +11348,7 @@
       <c r="AL247" s="3"/>
       <c r="AM247" s="3"/>
       <c r="AN247" s="3"/>
+      <c r="AO247" s="3"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="3"/>
@@ -11121,6 +11391,7 @@
       <c r="AL248" s="3"/>
       <c r="AM248" s="3"/>
       <c r="AN248" s="3"/>
+      <c r="AO248" s="3"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="3"/>
@@ -11163,6 +11434,7 @@
       <c r="AL249" s="3"/>
       <c r="AM249" s="3"/>
       <c r="AN249" s="3"/>
+      <c r="AO249" s="3"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="3"/>
@@ -11205,6 +11477,7 @@
       <c r="AL250" s="3"/>
       <c r="AM250" s="3"/>
       <c r="AN250" s="3"/>
+      <c r="AO250" s="3"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="3"/>
@@ -11247,6 +11520,7 @@
       <c r="AL251" s="3"/>
       <c r="AM251" s="3"/>
       <c r="AN251" s="3"/>
+      <c r="AO251" s="3"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="3"/>
@@ -11289,6 +11563,7 @@
       <c r="AL252" s="3"/>
       <c r="AM252" s="3"/>
       <c r="AN252" s="3"/>
+      <c r="AO252" s="3"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="3"/>
@@ -11331,6 +11606,7 @@
       <c r="AL253" s="3"/>
       <c r="AM253" s="3"/>
       <c r="AN253" s="3"/>
+      <c r="AO253" s="3"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="3"/>
@@ -11373,6 +11649,7 @@
       <c r="AL254" s="3"/>
       <c r="AM254" s="3"/>
       <c r="AN254" s="3"/>
+      <c r="AO254" s="3"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="3"/>
@@ -11415,6 +11692,7 @@
       <c r="AL255" s="3"/>
       <c r="AM255" s="3"/>
       <c r="AN255" s="3"/>
+      <c r="AO255" s="3"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="3"/>
@@ -11457,6 +11735,7 @@
       <c r="AL256" s="3"/>
       <c r="AM256" s="3"/>
       <c r="AN256" s="3"/>
+      <c r="AO256" s="3"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="3"/>
@@ -11499,6 +11778,7 @@
       <c r="AL257" s="3"/>
       <c r="AM257" s="3"/>
       <c r="AN257" s="3"/>
+      <c r="AO257" s="3"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="3"/>
@@ -11541,6 +11821,7 @@
       <c r="AL258" s="3"/>
       <c r="AM258" s="3"/>
       <c r="AN258" s="3"/>
+      <c r="AO258" s="3"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="3"/>
@@ -11583,6 +11864,7 @@
       <c r="AL259" s="3"/>
       <c r="AM259" s="3"/>
       <c r="AN259" s="3"/>
+      <c r="AO259" s="3"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="3"/>
@@ -11625,6 +11907,7 @@
       <c r="AL260" s="3"/>
       <c r="AM260" s="3"/>
       <c r="AN260" s="3"/>
+      <c r="AO260" s="3"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="3"/>
@@ -11667,6 +11950,7 @@
       <c r="AL261" s="3"/>
       <c r="AM261" s="3"/>
       <c r="AN261" s="3"/>
+      <c r="AO261" s="3"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="3"/>
@@ -11709,6 +11993,7 @@
       <c r="AL262" s="3"/>
       <c r="AM262" s="3"/>
       <c r="AN262" s="3"/>
+      <c r="AO262" s="3"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="3"/>
@@ -11751,6 +12036,7 @@
       <c r="AL263" s="3"/>
       <c r="AM263" s="3"/>
       <c r="AN263" s="3"/>
+      <c r="AO263" s="3"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="3"/>
@@ -11793,6 +12079,7 @@
       <c r="AL264" s="3"/>
       <c r="AM264" s="3"/>
       <c r="AN264" s="3"/>
+      <c r="AO264" s="3"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="3"/>
@@ -11835,6 +12122,7 @@
       <c r="AL265" s="3"/>
       <c r="AM265" s="3"/>
       <c r="AN265" s="3"/>
+      <c r="AO265" s="3"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="3"/>
@@ -11877,6 +12165,7 @@
       <c r="AL266" s="3"/>
       <c r="AM266" s="3"/>
       <c r="AN266" s="3"/>
+      <c r="AO266" s="3"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="3"/>
@@ -11919,6 +12208,7 @@
       <c r="AL267" s="3"/>
       <c r="AM267" s="3"/>
       <c r="AN267" s="3"/>
+      <c r="AO267" s="3"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="3"/>
@@ -11961,6 +12251,7 @@
       <c r="AL268" s="3"/>
       <c r="AM268" s="3"/>
       <c r="AN268" s="3"/>
+      <c r="AO268" s="3"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="3"/>
@@ -12003,6 +12294,7 @@
       <c r="AL269" s="3"/>
       <c r="AM269" s="3"/>
       <c r="AN269" s="3"/>
+      <c r="AO269" s="3"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="3"/>
@@ -12045,6 +12337,7 @@
       <c r="AL270" s="3"/>
       <c r="AM270" s="3"/>
       <c r="AN270" s="3"/>
+      <c r="AO270" s="3"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="3"/>
@@ -12087,6 +12380,7 @@
       <c r="AL271" s="3"/>
       <c r="AM271" s="3"/>
       <c r="AN271" s="3"/>
+      <c r="AO271" s="3"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="3"/>
@@ -12129,6 +12423,7 @@
       <c r="AL272" s="3"/>
       <c r="AM272" s="3"/>
       <c r="AN272" s="3"/>
+      <c r="AO272" s="3"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="3"/>
@@ -12171,6 +12466,7 @@
       <c r="AL273" s="3"/>
       <c r="AM273" s="3"/>
       <c r="AN273" s="3"/>
+      <c r="AO273" s="3"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="3"/>
@@ -12213,6 +12509,7 @@
       <c r="AL274" s="3"/>
       <c r="AM274" s="3"/>
       <c r="AN274" s="3"/>
+      <c r="AO274" s="3"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="3"/>
@@ -12255,6 +12552,7 @@
       <c r="AL275" s="3"/>
       <c r="AM275" s="3"/>
       <c r="AN275" s="3"/>
+      <c r="AO275" s="3"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="3"/>
@@ -12297,6 +12595,7 @@
       <c r="AL276" s="3"/>
       <c r="AM276" s="3"/>
       <c r="AN276" s="3"/>
+      <c r="AO276" s="3"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="3"/>
@@ -12339,6 +12638,7 @@
       <c r="AL277" s="3"/>
       <c r="AM277" s="3"/>
       <c r="AN277" s="3"/>
+      <c r="AO277" s="3"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="3"/>
@@ -12381,6 +12681,7 @@
       <c r="AL278" s="3"/>
       <c r="AM278" s="3"/>
       <c r="AN278" s="3"/>
+      <c r="AO278" s="3"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="3"/>
@@ -12423,6 +12724,7 @@
       <c r="AL279" s="3"/>
       <c r="AM279" s="3"/>
       <c r="AN279" s="3"/>
+      <c r="AO279" s="3"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="3"/>
@@ -12465,6 +12767,7 @@
       <c r="AL280" s="3"/>
       <c r="AM280" s="3"/>
       <c r="AN280" s="3"/>
+      <c r="AO280" s="3"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="3"/>
@@ -12507,6 +12810,7 @@
       <c r="AL281" s="3"/>
       <c r="AM281" s="3"/>
       <c r="AN281" s="3"/>
+      <c r="AO281" s="3"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="3"/>
@@ -12549,6 +12853,7 @@
       <c r="AL282" s="3"/>
       <c r="AM282" s="3"/>
       <c r="AN282" s="3"/>
+      <c r="AO282" s="3"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="3"/>
@@ -12591,6 +12896,7 @@
       <c r="AL283" s="3"/>
       <c r="AM283" s="3"/>
       <c r="AN283" s="3"/>
+      <c r="AO283" s="3"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="3"/>
@@ -12633,6 +12939,7 @@
       <c r="AL284" s="3"/>
       <c r="AM284" s="3"/>
       <c r="AN284" s="3"/>
+      <c r="AO284" s="3"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="3"/>
@@ -12675,6 +12982,7 @@
       <c r="AL285" s="3"/>
       <c r="AM285" s="3"/>
       <c r="AN285" s="3"/>
+      <c r="AO285" s="3"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="3"/>
@@ -12717,6 +13025,7 @@
       <c r="AL286" s="3"/>
       <c r="AM286" s="3"/>
       <c r="AN286" s="3"/>
+      <c r="AO286" s="3"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="3"/>
@@ -12759,6 +13068,7 @@
       <c r="AL287" s="3"/>
       <c r="AM287" s="3"/>
       <c r="AN287" s="3"/>
+      <c r="AO287" s="3"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="3"/>
@@ -12801,6 +13111,7 @@
       <c r="AL288" s="3"/>
       <c r="AM288" s="3"/>
       <c r="AN288" s="3"/>
+      <c r="AO288" s="3"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="3"/>
@@ -12843,6 +13154,7 @@
       <c r="AL289" s="3"/>
       <c r="AM289" s="3"/>
       <c r="AN289" s="3"/>
+      <c r="AO289" s="3"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="3"/>
@@ -12885,6 +13197,7 @@
       <c r="AL290" s="3"/>
       <c r="AM290" s="3"/>
       <c r="AN290" s="3"/>
+      <c r="AO290" s="3"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="3"/>
@@ -12927,6 +13240,7 @@
       <c r="AL291" s="3"/>
       <c r="AM291" s="3"/>
       <c r="AN291" s="3"/>
+      <c r="AO291" s="3"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="3"/>
@@ -12969,6 +13283,7 @@
       <c r="AL292" s="3"/>
       <c r="AM292" s="3"/>
       <c r="AN292" s="3"/>
+      <c r="AO292" s="3"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="3"/>
@@ -13011,6 +13326,7 @@
       <c r="AL293" s="3"/>
       <c r="AM293" s="3"/>
       <c r="AN293" s="3"/>
+      <c r="AO293" s="3"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="3"/>
@@ -13053,6 +13369,7 @@
       <c r="AL294" s="3"/>
       <c r="AM294" s="3"/>
       <c r="AN294" s="3"/>
+      <c r="AO294" s="3"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="3"/>
@@ -13095,6 +13412,7 @@
       <c r="AL295" s="3"/>
       <c r="AM295" s="3"/>
       <c r="AN295" s="3"/>
+      <c r="AO295" s="3"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="3"/>
@@ -13137,6 +13455,7 @@
       <c r="AL296" s="3"/>
       <c r="AM296" s="3"/>
       <c r="AN296" s="3"/>
+      <c r="AO296" s="3"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="3"/>
@@ -13179,6 +13498,7 @@
       <c r="AL297" s="3"/>
       <c r="AM297" s="3"/>
       <c r="AN297" s="3"/>
+      <c r="AO297" s="3"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="3"/>
@@ -13221,6 +13541,7 @@
       <c r="AL298" s="3"/>
       <c r="AM298" s="3"/>
       <c r="AN298" s="3"/>
+      <c r="AO298" s="3"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="3"/>
@@ -13263,6 +13584,7 @@
       <c r="AL299" s="3"/>
       <c r="AM299" s="3"/>
       <c r="AN299" s="3"/>
+      <c r="AO299" s="3"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="3"/>
@@ -13305,6 +13627,7 @@
       <c r="AL300" s="3"/>
       <c r="AM300" s="3"/>
       <c r="AN300" s="3"/>
+      <c r="AO300" s="3"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="3"/>
@@ -13347,6 +13670,7 @@
       <c r="AL301" s="3"/>
       <c r="AM301" s="3"/>
       <c r="AN301" s="3"/>
+      <c r="AO301" s="3"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="3"/>
@@ -13389,6 +13713,7 @@
       <c r="AL302" s="3"/>
       <c r="AM302" s="3"/>
       <c r="AN302" s="3"/>
+      <c r="AO302" s="3"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="3"/>
@@ -13431,6 +13756,7 @@
       <c r="AL303" s="3"/>
       <c r="AM303" s="3"/>
       <c r="AN303" s="3"/>
+      <c r="AO303" s="3"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="3"/>
@@ -13473,6 +13799,7 @@
       <c r="AL304" s="3"/>
       <c r="AM304" s="3"/>
       <c r="AN304" s="3"/>
+      <c r="AO304" s="3"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="3"/>
@@ -13515,6 +13842,7 @@
       <c r="AL305" s="3"/>
       <c r="AM305" s="3"/>
       <c r="AN305" s="3"/>
+      <c r="AO305" s="3"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="3"/>
@@ -13557,6 +13885,7 @@
       <c r="AL306" s="3"/>
       <c r="AM306" s="3"/>
       <c r="AN306" s="3"/>
+      <c r="AO306" s="3"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="3"/>
@@ -13599,6 +13928,7 @@
       <c r="AL307" s="3"/>
       <c r="AM307" s="3"/>
       <c r="AN307" s="3"/>
+      <c r="AO307" s="3"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="3"/>
@@ -13641,6 +13971,7 @@
       <c r="AL308" s="3"/>
       <c r="AM308" s="3"/>
       <c r="AN308" s="3"/>
+      <c r="AO308" s="3"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="3"/>
@@ -13683,6 +14014,7 @@
       <c r="AL309" s="3"/>
       <c r="AM309" s="3"/>
       <c r="AN309" s="3"/>
+      <c r="AO309" s="3"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="3"/>
@@ -13725,6 +14057,7 @@
       <c r="AL310" s="3"/>
       <c r="AM310" s="3"/>
       <c r="AN310" s="3"/>
+      <c r="AO310" s="3"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="3"/>
@@ -13767,6 +14100,7 @@
       <c r="AL311" s="3"/>
       <c r="AM311" s="3"/>
       <c r="AN311" s="3"/>
+      <c r="AO311" s="3"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="3"/>
@@ -13809,6 +14143,7 @@
       <c r="AL312" s="3"/>
       <c r="AM312" s="3"/>
       <c r="AN312" s="3"/>
+      <c r="AO312" s="3"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="3"/>
@@ -13851,6 +14186,7 @@
       <c r="AL313" s="3"/>
       <c r="AM313" s="3"/>
       <c r="AN313" s="3"/>
+      <c r="AO313" s="3"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="3"/>
@@ -13893,6 +14229,7 @@
       <c r="AL314" s="3"/>
       <c r="AM314" s="3"/>
       <c r="AN314" s="3"/>
+      <c r="AO314" s="3"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="3"/>
@@ -13935,6 +14272,7 @@
       <c r="AL315" s="3"/>
       <c r="AM315" s="3"/>
       <c r="AN315" s="3"/>
+      <c r="AO315" s="3"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="3"/>
@@ -13977,6 +14315,7 @@
       <c r="AL316" s="3"/>
       <c r="AM316" s="3"/>
       <c r="AN316" s="3"/>
+      <c r="AO316" s="3"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="3"/>
@@ -14019,6 +14358,7 @@
       <c r="AL317" s="3"/>
       <c r="AM317" s="3"/>
       <c r="AN317" s="3"/>
+      <c r="AO317" s="3"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="3"/>
@@ -14061,6 +14401,7 @@
       <c r="AL318" s="3"/>
       <c r="AM318" s="3"/>
       <c r="AN318" s="3"/>
+      <c r="AO318" s="3"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="3"/>
@@ -14103,6 +14444,7 @@
       <c r="AL319" s="3"/>
       <c r="AM319" s="3"/>
       <c r="AN319" s="3"/>
+      <c r="AO319" s="3"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="3"/>
@@ -14145,6 +14487,7 @@
       <c r="AL320" s="3"/>
       <c r="AM320" s="3"/>
       <c r="AN320" s="3"/>
+      <c r="AO320" s="3"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="3"/>
@@ -14187,6 +14530,7 @@
       <c r="AL321" s="3"/>
       <c r="AM321" s="3"/>
       <c r="AN321" s="3"/>
+      <c r="AO321" s="3"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="3"/>
@@ -14229,6 +14573,7 @@
       <c r="AL322" s="3"/>
       <c r="AM322" s="3"/>
       <c r="AN322" s="3"/>
+      <c r="AO322" s="3"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="3"/>
@@ -14271,6 +14616,7 @@
       <c r="AL323" s="3"/>
       <c r="AM323" s="3"/>
       <c r="AN323" s="3"/>
+      <c r="AO323" s="3"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="3"/>
@@ -14313,6 +14659,7 @@
       <c r="AL324" s="3"/>
       <c r="AM324" s="3"/>
       <c r="AN324" s="3"/>
+      <c r="AO324" s="3"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="3"/>
@@ -14355,6 +14702,7 @@
       <c r="AL325" s="3"/>
       <c r="AM325" s="3"/>
       <c r="AN325" s="3"/>
+      <c r="AO325" s="3"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="3"/>
@@ -14397,6 +14745,7 @@
       <c r="AL326" s="3"/>
       <c r="AM326" s="3"/>
       <c r="AN326" s="3"/>
+      <c r="AO326" s="3"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="3"/>
@@ -14439,6 +14788,7 @@
       <c r="AL327" s="3"/>
       <c r="AM327" s="3"/>
       <c r="AN327" s="3"/>
+      <c r="AO327" s="3"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="3"/>
@@ -14481,6 +14831,7 @@
       <c r="AL328" s="3"/>
       <c r="AM328" s="3"/>
       <c r="AN328" s="3"/>
+      <c r="AO328" s="3"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="3"/>
@@ -14523,6 +14874,7 @@
       <c r="AL329" s="3"/>
       <c r="AM329" s="3"/>
       <c r="AN329" s="3"/>
+      <c r="AO329" s="3"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="3"/>
@@ -14565,6 +14917,7 @@
       <c r="AL330" s="3"/>
       <c r="AM330" s="3"/>
       <c r="AN330" s="3"/>
+      <c r="AO330" s="3"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="3"/>
@@ -14607,6 +14960,7 @@
       <c r="AL331" s="3"/>
       <c r="AM331" s="3"/>
       <c r="AN331" s="3"/>
+      <c r="AO331" s="3"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="3"/>
@@ -14649,6 +15003,7 @@
       <c r="AL332" s="3"/>
       <c r="AM332" s="3"/>
       <c r="AN332" s="3"/>
+      <c r="AO332" s="3"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="3"/>
@@ -14691,6 +15046,7 @@
       <c r="AL333" s="3"/>
       <c r="AM333" s="3"/>
       <c r="AN333" s="3"/>
+      <c r="AO333" s="3"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="3"/>
@@ -14733,6 +15089,7 @@
       <c r="AL334" s="3"/>
       <c r="AM334" s="3"/>
       <c r="AN334" s="3"/>
+      <c r="AO334" s="3"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="3"/>
@@ -14775,6 +15132,7 @@
       <c r="AL335" s="3"/>
       <c r="AM335" s="3"/>
       <c r="AN335" s="3"/>
+      <c r="AO335" s="3"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="3"/>
@@ -14817,6 +15175,7 @@
       <c r="AL336" s="3"/>
       <c r="AM336" s="3"/>
       <c r="AN336" s="3"/>
+      <c r="AO336" s="3"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="3"/>
@@ -14859,6 +15218,7 @@
       <c r="AL337" s="3"/>
       <c r="AM337" s="3"/>
       <c r="AN337" s="3"/>
+      <c r="AO337" s="3"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="3"/>
@@ -14901,6 +15261,7 @@
       <c r="AL338" s="3"/>
       <c r="AM338" s="3"/>
       <c r="AN338" s="3"/>
+      <c r="AO338" s="3"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="3"/>
@@ -14943,6 +15304,7 @@
       <c r="AL339" s="3"/>
       <c r="AM339" s="3"/>
       <c r="AN339" s="3"/>
+      <c r="AO339" s="3"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="3"/>
@@ -14985,6 +15347,7 @@
       <c r="AL340" s="3"/>
       <c r="AM340" s="3"/>
       <c r="AN340" s="3"/>
+      <c r="AO340" s="3"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="3"/>
@@ -15027,6 +15390,7 @@
       <c r="AL341" s="3"/>
       <c r="AM341" s="3"/>
       <c r="AN341" s="3"/>
+      <c r="AO341" s="3"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="3"/>
@@ -15069,6 +15433,7 @@
       <c r="AL342" s="3"/>
       <c r="AM342" s="3"/>
       <c r="AN342" s="3"/>
+      <c r="AO342" s="3"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="3"/>
@@ -15111,6 +15476,7 @@
       <c r="AL343" s="3"/>
       <c r="AM343" s="3"/>
       <c r="AN343" s="3"/>
+      <c r="AO343" s="3"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="3"/>
@@ -15153,6 +15519,7 @@
       <c r="AL344" s="3"/>
       <c r="AM344" s="3"/>
       <c r="AN344" s="3"/>
+      <c r="AO344" s="3"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="3"/>
@@ -15195,6 +15562,7 @@
       <c r="AL345" s="3"/>
       <c r="AM345" s="3"/>
       <c r="AN345" s="3"/>
+      <c r="AO345" s="3"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="3"/>
@@ -15237,6 +15605,7 @@
       <c r="AL346" s="3"/>
       <c r="AM346" s="3"/>
       <c r="AN346" s="3"/>
+      <c r="AO346" s="3"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="3"/>
@@ -15279,6 +15648,7 @@
       <c r="AL347" s="3"/>
       <c r="AM347" s="3"/>
       <c r="AN347" s="3"/>
+      <c r="AO347" s="3"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="3"/>
@@ -15321,6 +15691,7 @@
       <c r="AL348" s="3"/>
       <c r="AM348" s="3"/>
       <c r="AN348" s="3"/>
+      <c r="AO348" s="3"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="3"/>
@@ -15363,6 +15734,7 @@
       <c r="AL349" s="3"/>
       <c r="AM349" s="3"/>
       <c r="AN349" s="3"/>
+      <c r="AO349" s="3"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="3"/>
@@ -15405,6 +15777,7 @@
       <c r="AL350" s="3"/>
       <c r="AM350" s="3"/>
       <c r="AN350" s="3"/>
+      <c r="AO350" s="3"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="3"/>
@@ -15447,6 +15820,7 @@
       <c r="AL351" s="3"/>
       <c r="AM351" s="3"/>
       <c r="AN351" s="3"/>
+      <c r="AO351" s="3"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="3"/>
@@ -15489,6 +15863,7 @@
       <c r="AL352" s="3"/>
       <c r="AM352" s="3"/>
       <c r="AN352" s="3"/>
+      <c r="AO352" s="3"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="3"/>
@@ -15531,6 +15906,7 @@
       <c r="AL353" s="3"/>
       <c r="AM353" s="3"/>
       <c r="AN353" s="3"/>
+      <c r="AO353" s="3"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="3"/>
@@ -15573,6 +15949,7 @@
       <c r="AL354" s="3"/>
       <c r="AM354" s="3"/>
       <c r="AN354" s="3"/>
+      <c r="AO354" s="3"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="3"/>
@@ -15615,6 +15992,7 @@
       <c r="AL355" s="3"/>
       <c r="AM355" s="3"/>
       <c r="AN355" s="3"/>
+      <c r="AO355" s="3"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="3"/>
@@ -15657,6 +16035,7 @@
       <c r="AL356" s="3"/>
       <c r="AM356" s="3"/>
       <c r="AN356" s="3"/>
+      <c r="AO356" s="3"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="3"/>
@@ -15699,6 +16078,7 @@
       <c r="AL357" s="3"/>
       <c r="AM357" s="3"/>
       <c r="AN357" s="3"/>
+      <c r="AO357" s="3"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="3"/>
@@ -15741,6 +16121,7 @@
       <c r="AL358" s="3"/>
       <c r="AM358" s="3"/>
       <c r="AN358" s="3"/>
+      <c r="AO358" s="3"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="3"/>
@@ -15783,6 +16164,7 @@
       <c r="AL359" s="3"/>
       <c r="AM359" s="3"/>
       <c r="AN359" s="3"/>
+      <c r="AO359" s="3"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="3"/>
@@ -15825,6 +16207,7 @@
       <c r="AL360" s="3"/>
       <c r="AM360" s="3"/>
       <c r="AN360" s="3"/>
+      <c r="AO360" s="3"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="3"/>
@@ -15867,6 +16250,7 @@
       <c r="AL361" s="3"/>
       <c r="AM361" s="3"/>
       <c r="AN361" s="3"/>
+      <c r="AO361" s="3"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="3"/>
@@ -15909,6 +16293,7 @@
       <c r="AL362" s="3"/>
       <c r="AM362" s="3"/>
       <c r="AN362" s="3"/>
+      <c r="AO362" s="3"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="3"/>
@@ -15951,6 +16336,7 @@
       <c r="AL363" s="3"/>
       <c r="AM363" s="3"/>
       <c r="AN363" s="3"/>
+      <c r="AO363" s="3"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="3"/>
@@ -15993,6 +16379,7 @@
       <c r="AL364" s="3"/>
       <c r="AM364" s="3"/>
       <c r="AN364" s="3"/>
+      <c r="AO364" s="3"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="3"/>
@@ -16035,6 +16422,7 @@
       <c r="AL365" s="3"/>
       <c r="AM365" s="3"/>
       <c r="AN365" s="3"/>
+      <c r="AO365" s="3"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="3"/>
@@ -16077,6 +16465,7 @@
       <c r="AL366" s="3"/>
       <c r="AM366" s="3"/>
       <c r="AN366" s="3"/>
+      <c r="AO366" s="3"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="3"/>
@@ -16119,6 +16508,7 @@
       <c r="AL367" s="3"/>
       <c r="AM367" s="3"/>
       <c r="AN367" s="3"/>
+      <c r="AO367" s="3"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="3"/>
@@ -16161,6 +16551,7 @@
       <c r="AL368" s="3"/>
       <c r="AM368" s="3"/>
       <c r="AN368" s="3"/>
+      <c r="AO368" s="3"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="3"/>
@@ -16203,6 +16594,7 @@
       <c r="AL369" s="3"/>
       <c r="AM369" s="3"/>
       <c r="AN369" s="3"/>
+      <c r="AO369" s="3"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="3"/>
@@ -16245,6 +16637,7 @@
       <c r="AL370" s="3"/>
       <c r="AM370" s="3"/>
       <c r="AN370" s="3"/>
+      <c r="AO370" s="3"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="3"/>
@@ -16287,6 +16680,7 @@
       <c r="AL371" s="3"/>
       <c r="AM371" s="3"/>
       <c r="AN371" s="3"/>
+      <c r="AO371" s="3"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="3"/>
@@ -16329,6 +16723,7 @@
       <c r="AL372" s="3"/>
       <c r="AM372" s="3"/>
       <c r="AN372" s="3"/>
+      <c r="AO372" s="3"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="3"/>
@@ -16371,6 +16766,7 @@
       <c r="AL373" s="3"/>
       <c r="AM373" s="3"/>
       <c r="AN373" s="3"/>
+      <c r="AO373" s="3"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="3"/>
@@ -16413,6 +16809,7 @@
       <c r="AL374" s="3"/>
       <c r="AM374" s="3"/>
       <c r="AN374" s="3"/>
+      <c r="AO374" s="3"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="3"/>
@@ -16455,6 +16852,7 @@
       <c r="AL375" s="3"/>
       <c r="AM375" s="3"/>
       <c r="AN375" s="3"/>
+      <c r="AO375" s="3"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="3"/>
@@ -16497,6 +16895,7 @@
       <c r="AL376" s="3"/>
       <c r="AM376" s="3"/>
       <c r="AN376" s="3"/>
+      <c r="AO376" s="3"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="3"/>
@@ -16539,6 +16938,7 @@
       <c r="AL377" s="3"/>
       <c r="AM377" s="3"/>
       <c r="AN377" s="3"/>
+      <c r="AO377" s="3"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="3"/>
@@ -16581,6 +16981,7 @@
       <c r="AL378" s="3"/>
       <c r="AM378" s="3"/>
       <c r="AN378" s="3"/>
+      <c r="AO378" s="3"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="3"/>
@@ -16623,6 +17024,7 @@
       <c r="AL379" s="3"/>
       <c r="AM379" s="3"/>
       <c r="AN379" s="3"/>
+      <c r="AO379" s="3"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="3"/>
@@ -16665,6 +17067,7 @@
       <c r="AL380" s="3"/>
       <c r="AM380" s="3"/>
       <c r="AN380" s="3"/>
+      <c r="AO380" s="3"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="3"/>
@@ -16707,6 +17110,7 @@
       <c r="AL381" s="3"/>
       <c r="AM381" s="3"/>
       <c r="AN381" s="3"/>
+      <c r="AO381" s="3"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="3"/>
@@ -16749,6 +17153,7 @@
       <c r="AL382" s="3"/>
       <c r="AM382" s="3"/>
       <c r="AN382" s="3"/>
+      <c r="AO382" s="3"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="3"/>
@@ -16791,6 +17196,7 @@
       <c r="AL383" s="3"/>
       <c r="AM383" s="3"/>
       <c r="AN383" s="3"/>
+      <c r="AO383" s="3"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="3"/>
@@ -16833,6 +17239,7 @@
       <c r="AL384" s="3"/>
       <c r="AM384" s="3"/>
       <c r="AN384" s="3"/>
+      <c r="AO384" s="3"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="3"/>
@@ -16875,6 +17282,7 @@
       <c r="AL385" s="3"/>
       <c r="AM385" s="3"/>
       <c r="AN385" s="3"/>
+      <c r="AO385" s="3"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="3"/>
@@ -16917,6 +17325,7 @@
       <c r="AL386" s="3"/>
       <c r="AM386" s="3"/>
       <c r="AN386" s="3"/>
+      <c r="AO386" s="3"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="3"/>
@@ -16959,6 +17368,7 @@
       <c r="AL387" s="3"/>
       <c r="AM387" s="3"/>
       <c r="AN387" s="3"/>
+      <c r="AO387" s="3"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="3"/>
@@ -17001,6 +17411,7 @@
       <c r="AL388" s="3"/>
       <c r="AM388" s="3"/>
       <c r="AN388" s="3"/>
+      <c r="AO388" s="3"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="3"/>
@@ -17043,6 +17454,7 @@
       <c r="AL389" s="3"/>
       <c r="AM389" s="3"/>
       <c r="AN389" s="3"/>
+      <c r="AO389" s="3"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="3"/>
@@ -17085,6 +17497,7 @@
       <c r="AL390" s="3"/>
       <c r="AM390" s="3"/>
       <c r="AN390" s="3"/>
+      <c r="AO390" s="3"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="3"/>
@@ -17127,6 +17540,7 @@
       <c r="AL391" s="3"/>
       <c r="AM391" s="3"/>
       <c r="AN391" s="3"/>
+      <c r="AO391" s="3"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="3"/>
@@ -17169,6 +17583,7 @@
       <c r="AL392" s="3"/>
       <c r="AM392" s="3"/>
       <c r="AN392" s="3"/>
+      <c r="AO392" s="3"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="3"/>
@@ -17211,6 +17626,7 @@
       <c r="AL393" s="3"/>
       <c r="AM393" s="3"/>
       <c r="AN393" s="3"/>
+      <c r="AO393" s="3"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="3"/>
@@ -17253,6 +17669,7 @@
       <c r="AL394" s="3"/>
       <c r="AM394" s="3"/>
       <c r="AN394" s="3"/>
+      <c r="AO394" s="3"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="3"/>
@@ -17295,6 +17712,7 @@
       <c r="AL395" s="3"/>
       <c r="AM395" s="3"/>
       <c r="AN395" s="3"/>
+      <c r="AO395" s="3"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="3"/>
@@ -17337,6 +17755,7 @@
       <c r="AL396" s="3"/>
       <c r="AM396" s="3"/>
       <c r="AN396" s="3"/>
+      <c r="AO396" s="3"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="3"/>
@@ -17379,6 +17798,7 @@
       <c r="AL397" s="3"/>
       <c r="AM397" s="3"/>
       <c r="AN397" s="3"/>
+      <c r="AO397" s="3"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="3"/>
@@ -17421,6 +17841,7 @@
       <c r="AL398" s="3"/>
       <c r="AM398" s="3"/>
       <c r="AN398" s="3"/>
+      <c r="AO398" s="3"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="3"/>
@@ -17463,6 +17884,7 @@
       <c r="AL399" s="3"/>
       <c r="AM399" s="3"/>
       <c r="AN399" s="3"/>
+      <c r="AO399" s="3"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="3"/>
@@ -17505,6 +17927,7 @@
       <c r="AL400" s="3"/>
       <c r="AM400" s="3"/>
       <c r="AN400" s="3"/>
+      <c r="AO400" s="3"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="3"/>
@@ -17547,6 +17970,7 @@
       <c r="AL401" s="3"/>
       <c r="AM401" s="3"/>
       <c r="AN401" s="3"/>
+      <c r="AO401" s="3"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="3"/>
@@ -17589,6 +18013,7 @@
       <c r="AL402" s="3"/>
       <c r="AM402" s="3"/>
       <c r="AN402" s="3"/>
+      <c r="AO402" s="3"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="3"/>
@@ -17631,6 +18056,7 @@
       <c r="AL403" s="3"/>
       <c r="AM403" s="3"/>
       <c r="AN403" s="3"/>
+      <c r="AO403" s="3"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="3"/>
@@ -17673,6 +18099,7 @@
       <c r="AL404" s="3"/>
       <c r="AM404" s="3"/>
       <c r="AN404" s="3"/>
+      <c r="AO404" s="3"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="3"/>
@@ -17715,6 +18142,7 @@
       <c r="AL405" s="3"/>
       <c r="AM405" s="3"/>
       <c r="AN405" s="3"/>
+      <c r="AO405" s="3"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="3"/>
@@ -17757,6 +18185,7 @@
       <c r="AL406" s="3"/>
       <c r="AM406" s="3"/>
       <c r="AN406" s="3"/>
+      <c r="AO406" s="3"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="3"/>
@@ -17799,6 +18228,7 @@
       <c r="AL407" s="3"/>
       <c r="AM407" s="3"/>
       <c r="AN407" s="3"/>
+      <c r="AO407" s="3"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="3"/>
@@ -17841,6 +18271,7 @@
       <c r="AL408" s="3"/>
       <c r="AM408" s="3"/>
       <c r="AN408" s="3"/>
+      <c r="AO408" s="3"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="3"/>
@@ -17883,6 +18314,7 @@
       <c r="AL409" s="3"/>
       <c r="AM409" s="3"/>
       <c r="AN409" s="3"/>
+      <c r="AO409" s="3"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="3"/>
@@ -17925,6 +18357,7 @@
       <c r="AL410" s="3"/>
       <c r="AM410" s="3"/>
       <c r="AN410" s="3"/>
+      <c r="AO410" s="3"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="3"/>
@@ -17967,6 +18400,7 @@
       <c r="AL411" s="3"/>
       <c r="AM411" s="3"/>
       <c r="AN411" s="3"/>
+      <c r="AO411" s="3"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="3"/>
@@ -18009,6 +18443,7 @@
       <c r="AL412" s="3"/>
       <c r="AM412" s="3"/>
       <c r="AN412" s="3"/>
+      <c r="AO412" s="3"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="3"/>
@@ -18051,6 +18486,7 @@
       <c r="AL413" s="3"/>
       <c r="AM413" s="3"/>
       <c r="AN413" s="3"/>
+      <c r="AO413" s="3"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="3"/>
@@ -18093,6 +18529,7 @@
       <c r="AL414" s="3"/>
       <c r="AM414" s="3"/>
       <c r="AN414" s="3"/>
+      <c r="AO414" s="3"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="3"/>
@@ -18135,6 +18572,7 @@
       <c r="AL415" s="3"/>
       <c r="AM415" s="3"/>
       <c r="AN415" s="3"/>
+      <c r="AO415" s="3"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="3"/>
@@ -18177,6 +18615,7 @@
       <c r="AL416" s="3"/>
       <c r="AM416" s="3"/>
       <c r="AN416" s="3"/>
+      <c r="AO416" s="3"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="3"/>
@@ -18219,6 +18658,7 @@
       <c r="AL417" s="3"/>
       <c r="AM417" s="3"/>
       <c r="AN417" s="3"/>
+      <c r="AO417" s="3"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="3"/>
@@ -18261,6 +18701,7 @@
       <c r="AL418" s="3"/>
       <c r="AM418" s="3"/>
       <c r="AN418" s="3"/>
+      <c r="AO418" s="3"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="3"/>
@@ -18303,6 +18744,7 @@
       <c r="AL419" s="3"/>
       <c r="AM419" s="3"/>
       <c r="AN419" s="3"/>
+      <c r="AO419" s="3"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="3"/>
@@ -18345,6 +18787,7 @@
       <c r="AL420" s="3"/>
       <c r="AM420" s="3"/>
       <c r="AN420" s="3"/>
+      <c r="AO420" s="3"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="3"/>
@@ -18387,6 +18830,7 @@
       <c r="AL421" s="3"/>
       <c r="AM421" s="3"/>
       <c r="AN421" s="3"/>
+      <c r="AO421" s="3"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="3"/>
@@ -18429,6 +18873,7 @@
       <c r="AL422" s="3"/>
       <c r="AM422" s="3"/>
       <c r="AN422" s="3"/>
+      <c r="AO422" s="3"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="3"/>
@@ -18471,6 +18916,7 @@
       <c r="AL423" s="3"/>
       <c r="AM423" s="3"/>
       <c r="AN423" s="3"/>
+      <c r="AO423" s="3"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="3"/>
@@ -18513,6 +18959,7 @@
       <c r="AL424" s="3"/>
       <c r="AM424" s="3"/>
       <c r="AN424" s="3"/>
+      <c r="AO424" s="3"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="3"/>
@@ -18555,6 +19002,7 @@
       <c r="AL425" s="3"/>
       <c r="AM425" s="3"/>
       <c r="AN425" s="3"/>
+      <c r="AO425" s="3"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="3"/>
@@ -18597,6 +19045,7 @@
       <c r="AL426" s="3"/>
       <c r="AM426" s="3"/>
       <c r="AN426" s="3"/>
+      <c r="AO426" s="3"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="3"/>
@@ -18639,6 +19088,7 @@
       <c r="AL427" s="3"/>
       <c r="AM427" s="3"/>
       <c r="AN427" s="3"/>
+      <c r="AO427" s="3"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="3"/>
@@ -18681,6 +19131,7 @@
       <c r="AL428" s="3"/>
       <c r="AM428" s="3"/>
       <c r="AN428" s="3"/>
+      <c r="AO428" s="3"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="3"/>
@@ -18723,6 +19174,7 @@
       <c r="AL429" s="3"/>
       <c r="AM429" s="3"/>
       <c r="AN429" s="3"/>
+      <c r="AO429" s="3"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="3"/>
@@ -18765,6 +19217,7 @@
       <c r="AL430" s="3"/>
       <c r="AM430" s="3"/>
       <c r="AN430" s="3"/>
+      <c r="AO430" s="3"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="3"/>
@@ -18807,6 +19260,7 @@
       <c r="AL431" s="3"/>
       <c r="AM431" s="3"/>
       <c r="AN431" s="3"/>
+      <c r="AO431" s="3"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="3"/>
@@ -18849,6 +19303,7 @@
       <c r="AL432" s="3"/>
       <c r="AM432" s="3"/>
       <c r="AN432" s="3"/>
+      <c r="AO432" s="3"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="3"/>
@@ -18891,6 +19346,7 @@
       <c r="AL433" s="3"/>
       <c r="AM433" s="3"/>
       <c r="AN433" s="3"/>
+      <c r="AO433" s="3"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="3"/>
@@ -18933,6 +19389,7 @@
       <c r="AL434" s="3"/>
       <c r="AM434" s="3"/>
       <c r="AN434" s="3"/>
+      <c r="AO434" s="3"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="3"/>
@@ -18975,6 +19432,7 @@
       <c r="AL435" s="3"/>
       <c r="AM435" s="3"/>
       <c r="AN435" s="3"/>
+      <c r="AO435" s="3"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="3"/>
@@ -19017,6 +19475,7 @@
       <c r="AL436" s="3"/>
       <c r="AM436" s="3"/>
       <c r="AN436" s="3"/>
+      <c r="AO436" s="3"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="3"/>
@@ -19059,6 +19518,7 @@
       <c r="AL437" s="3"/>
       <c r="AM437" s="3"/>
       <c r="AN437" s="3"/>
+      <c r="AO437" s="3"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="3"/>
@@ -19101,6 +19561,7 @@
       <c r="AL438" s="3"/>
       <c r="AM438" s="3"/>
       <c r="AN438" s="3"/>
+      <c r="AO438" s="3"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="3"/>
@@ -19143,6 +19604,7 @@
       <c r="AL439" s="3"/>
       <c r="AM439" s="3"/>
       <c r="AN439" s="3"/>
+      <c r="AO439" s="3"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="3"/>
@@ -19185,6 +19647,7 @@
       <c r="AL440" s="3"/>
       <c r="AM440" s="3"/>
       <c r="AN440" s="3"/>
+      <c r="AO440" s="3"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="3"/>
@@ -19227,6 +19690,7 @@
       <c r="AL441" s="3"/>
       <c r="AM441" s="3"/>
       <c r="AN441" s="3"/>
+      <c r="AO441" s="3"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="3"/>
@@ -19269,6 +19733,7 @@
       <c r="AL442" s="3"/>
       <c r="AM442" s="3"/>
       <c r="AN442" s="3"/>
+      <c r="AO442" s="3"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="3"/>
@@ -19311,6 +19776,7 @@
       <c r="AL443" s="3"/>
       <c r="AM443" s="3"/>
       <c r="AN443" s="3"/>
+      <c r="AO443" s="3"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="3"/>
@@ -19353,6 +19819,7 @@
       <c r="AL444" s="3"/>
       <c r="AM444" s="3"/>
       <c r="AN444" s="3"/>
+      <c r="AO444" s="3"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="3"/>
@@ -19395,6 +19862,7 @@
       <c r="AL445" s="3"/>
       <c r="AM445" s="3"/>
       <c r="AN445" s="3"/>
+      <c r="AO445" s="3"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="3"/>
@@ -19437,6 +19905,7 @@
       <c r="AL446" s="3"/>
       <c r="AM446" s="3"/>
       <c r="AN446" s="3"/>
+      <c r="AO446" s="3"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="3"/>
@@ -19479,6 +19948,7 @@
       <c r="AL447" s="3"/>
       <c r="AM447" s="3"/>
       <c r="AN447" s="3"/>
+      <c r="AO447" s="3"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="3"/>
@@ -19521,6 +19991,7 @@
       <c r="AL448" s="3"/>
       <c r="AM448" s="3"/>
       <c r="AN448" s="3"/>
+      <c r="AO448" s="3"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="3"/>
@@ -19563,6 +20034,7 @@
       <c r="AL449" s="3"/>
       <c r="AM449" s="3"/>
       <c r="AN449" s="3"/>
+      <c r="AO449" s="3"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="3"/>
@@ -19605,6 +20077,7 @@
       <c r="AL450" s="3"/>
       <c r="AM450" s="3"/>
       <c r="AN450" s="3"/>
+      <c r="AO450" s="3"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="3"/>
@@ -19647,6 +20120,7 @@
       <c r="AL451" s="3"/>
       <c r="AM451" s="3"/>
       <c r="AN451" s="3"/>
+      <c r="AO451" s="3"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="3"/>
@@ -19689,6 +20163,7 @@
       <c r="AL452" s="3"/>
       <c r="AM452" s="3"/>
       <c r="AN452" s="3"/>
+      <c r="AO452" s="3"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="3"/>
@@ -19731,6 +20206,7 @@
       <c r="AL453" s="3"/>
       <c r="AM453" s="3"/>
       <c r="AN453" s="3"/>
+      <c r="AO453" s="3"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="3"/>
@@ -19773,6 +20249,7 @@
       <c r="AL454" s="3"/>
       <c r="AM454" s="3"/>
       <c r="AN454" s="3"/>
+      <c r="AO454" s="3"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="3"/>
@@ -19815,6 +20292,7 @@
       <c r="AL455" s="3"/>
       <c r="AM455" s="3"/>
       <c r="AN455" s="3"/>
+      <c r="AO455" s="3"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="3"/>
@@ -19857,6 +20335,7 @@
       <c r="AL456" s="3"/>
       <c r="AM456" s="3"/>
       <c r="AN456" s="3"/>
+      <c r="AO456" s="3"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="3"/>
@@ -19899,6 +20378,7 @@
       <c r="AL457" s="3"/>
       <c r="AM457" s="3"/>
       <c r="AN457" s="3"/>
+      <c r="AO457" s="3"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="3"/>
@@ -19941,6 +20421,7 @@
       <c r="AL458" s="3"/>
       <c r="AM458" s="3"/>
       <c r="AN458" s="3"/>
+      <c r="AO458" s="3"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="3"/>
@@ -19983,6 +20464,7 @@
       <c r="AL459" s="3"/>
       <c r="AM459" s="3"/>
       <c r="AN459" s="3"/>
+      <c r="AO459" s="3"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="3"/>
@@ -20025,6 +20507,7 @@
       <c r="AL460" s="3"/>
       <c r="AM460" s="3"/>
       <c r="AN460" s="3"/>
+      <c r="AO460" s="3"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="3"/>
@@ -20067,6 +20550,7 @@
       <c r="AL461" s="3"/>
       <c r="AM461" s="3"/>
       <c r="AN461" s="3"/>
+      <c r="AO461" s="3"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="3"/>
@@ -20109,6 +20593,7 @@
       <c r="AL462" s="3"/>
       <c r="AM462" s="3"/>
       <c r="AN462" s="3"/>
+      <c r="AO462" s="3"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="3"/>
@@ -20151,6 +20636,7 @@
       <c r="AL463" s="3"/>
       <c r="AM463" s="3"/>
       <c r="AN463" s="3"/>
+      <c r="AO463" s="3"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="3"/>
@@ -20193,6 +20679,7 @@
       <c r="AL464" s="3"/>
       <c r="AM464" s="3"/>
       <c r="AN464" s="3"/>
+      <c r="AO464" s="3"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="3"/>
@@ -20235,6 +20722,7 @@
       <c r="AL465" s="3"/>
       <c r="AM465" s="3"/>
       <c r="AN465" s="3"/>
+      <c r="AO465" s="3"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="3"/>
@@ -20277,6 +20765,7 @@
       <c r="AL466" s="3"/>
       <c r="AM466" s="3"/>
       <c r="AN466" s="3"/>
+      <c r="AO466" s="3"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="3"/>
@@ -20319,6 +20808,7 @@
       <c r="AL467" s="3"/>
       <c r="AM467" s="3"/>
       <c r="AN467" s="3"/>
+      <c r="AO467" s="3"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="3"/>
@@ -20361,6 +20851,7 @@
       <c r="AL468" s="3"/>
       <c r="AM468" s="3"/>
       <c r="AN468" s="3"/>
+      <c r="AO468" s="3"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="3"/>
@@ -20403,6 +20894,7 @@
       <c r="AL469" s="3"/>
       <c r="AM469" s="3"/>
       <c r="AN469" s="3"/>
+      <c r="AO469" s="3"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="3"/>
@@ -20445,6 +20937,7 @@
       <c r="AL470" s="3"/>
       <c r="AM470" s="3"/>
       <c r="AN470" s="3"/>
+      <c r="AO470" s="3"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="3"/>
@@ -20487,6 +20980,7 @@
       <c r="AL471" s="3"/>
       <c r="AM471" s="3"/>
       <c r="AN471" s="3"/>
+      <c r="AO471" s="3"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="3"/>
@@ -20529,6 +21023,7 @@
       <c r="AL472" s="3"/>
       <c r="AM472" s="3"/>
       <c r="AN472" s="3"/>
+      <c r="AO472" s="3"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="3"/>
@@ -20571,6 +21066,7 @@
       <c r="AL473" s="3"/>
       <c r="AM473" s="3"/>
       <c r="AN473" s="3"/>
+      <c r="AO473" s="3"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="3"/>
@@ -20613,6 +21109,7 @@
       <c r="AL474" s="3"/>
       <c r="AM474" s="3"/>
       <c r="AN474" s="3"/>
+      <c r="AO474" s="3"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="3"/>
@@ -20655,6 +21152,7 @@
       <c r="AL475" s="3"/>
       <c r="AM475" s="3"/>
       <c r="AN475" s="3"/>
+      <c r="AO475" s="3"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="3"/>
@@ -20697,6 +21195,7 @@
       <c r="AL476" s="3"/>
       <c r="AM476" s="3"/>
       <c r="AN476" s="3"/>
+      <c r="AO476" s="3"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="3"/>
@@ -20739,6 +21238,7 @@
       <c r="AL477" s="3"/>
       <c r="AM477" s="3"/>
       <c r="AN477" s="3"/>
+      <c r="AO477" s="3"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="3"/>
@@ -20781,6 +21281,7 @@
       <c r="AL478" s="3"/>
       <c r="AM478" s="3"/>
       <c r="AN478" s="3"/>
+      <c r="AO478" s="3"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="3"/>
@@ -20823,6 +21324,7 @@
       <c r="AL479" s="3"/>
       <c r="AM479" s="3"/>
       <c r="AN479" s="3"/>
+      <c r="AO479" s="3"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="3"/>
@@ -20865,6 +21367,7 @@
       <c r="AL480" s="3"/>
       <c r="AM480" s="3"/>
       <c r="AN480" s="3"/>
+      <c r="AO480" s="3"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="3"/>
@@ -20907,6 +21410,7 @@
       <c r="AL481" s="3"/>
       <c r="AM481" s="3"/>
       <c r="AN481" s="3"/>
+      <c r="AO481" s="3"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="3"/>
@@ -20949,6 +21453,7 @@
       <c r="AL482" s="3"/>
       <c r="AM482" s="3"/>
       <c r="AN482" s="3"/>
+      <c r="AO482" s="3"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="3"/>
@@ -20991,6 +21496,7 @@
       <c r="AL483" s="3"/>
       <c r="AM483" s="3"/>
       <c r="AN483" s="3"/>
+      <c r="AO483" s="3"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="3"/>
@@ -21033,6 +21539,7 @@
       <c r="AL484" s="3"/>
       <c r="AM484" s="3"/>
       <c r="AN484" s="3"/>
+      <c r="AO484" s="3"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="3"/>
@@ -21075,6 +21582,7 @@
       <c r="AL485" s="3"/>
       <c r="AM485" s="3"/>
       <c r="AN485" s="3"/>
+      <c r="AO485" s="3"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="3"/>
@@ -21117,6 +21625,7 @@
       <c r="AL486" s="3"/>
       <c r="AM486" s="3"/>
       <c r="AN486" s="3"/>
+      <c r="AO486" s="3"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="3"/>
@@ -21159,6 +21668,7 @@
       <c r="AL487" s="3"/>
       <c r="AM487" s="3"/>
       <c r="AN487" s="3"/>
+      <c r="AO487" s="3"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="3"/>
@@ -21201,6 +21711,7 @@
       <c r="AL488" s="3"/>
       <c r="AM488" s="3"/>
       <c r="AN488" s="3"/>
+      <c r="AO488" s="3"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="3"/>
@@ -21243,6 +21754,7 @@
       <c r="AL489" s="3"/>
       <c r="AM489" s="3"/>
       <c r="AN489" s="3"/>
+      <c r="AO489" s="3"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="3"/>
@@ -21285,6 +21797,7 @@
       <c r="AL490" s="3"/>
       <c r="AM490" s="3"/>
       <c r="AN490" s="3"/>
+      <c r="AO490" s="3"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="3"/>
@@ -21327,6 +21840,7 @@
       <c r="AL491" s="3"/>
       <c r="AM491" s="3"/>
       <c r="AN491" s="3"/>
+      <c r="AO491" s="3"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="3"/>
@@ -21369,6 +21883,7 @@
       <c r="AL492" s="3"/>
       <c r="AM492" s="3"/>
       <c r="AN492" s="3"/>
+      <c r="AO492" s="3"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="3"/>
@@ -21411,6 +21926,7 @@
       <c r="AL493" s="3"/>
       <c r="AM493" s="3"/>
       <c r="AN493" s="3"/>
+      <c r="AO493" s="3"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="3"/>
@@ -21453,6 +21969,7 @@
       <c r="AL494" s="3"/>
       <c r="AM494" s="3"/>
       <c r="AN494" s="3"/>
+      <c r="AO494" s="3"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="3"/>
@@ -21495,6 +22012,7 @@
       <c r="AL495" s="3"/>
       <c r="AM495" s="3"/>
       <c r="AN495" s="3"/>
+      <c r="AO495" s="3"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="3"/>
@@ -21537,6 +22055,7 @@
       <c r="AL496" s="3"/>
       <c r="AM496" s="3"/>
       <c r="AN496" s="3"/>
+      <c r="AO496" s="3"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="3"/>
@@ -21579,6 +22098,7 @@
       <c r="AL497" s="3"/>
       <c r="AM497" s="3"/>
       <c r="AN497" s="3"/>
+      <c r="AO497" s="3"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="3"/>
@@ -21621,6 +22141,7 @@
       <c r="AL498" s="3"/>
       <c r="AM498" s="3"/>
       <c r="AN498" s="3"/>
+      <c r="AO498" s="3"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="3"/>
@@ -21663,6 +22184,7 @@
       <c r="AL499" s="3"/>
       <c r="AM499" s="3"/>
       <c r="AN499" s="3"/>
+      <c r="AO499" s="3"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="3"/>
@@ -21705,6 +22227,7 @@
       <c r="AL500" s="3"/>
       <c r="AM500" s="3"/>
       <c r="AN500" s="3"/>
+      <c r="AO500" s="3"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="3"/>
@@ -21747,6 +22270,7 @@
       <c r="AL501" s="3"/>
       <c r="AM501" s="3"/>
       <c r="AN501" s="3"/>
+      <c r="AO501" s="3"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="3"/>
@@ -21789,6 +22313,7 @@
       <c r="AL502" s="3"/>
       <c r="AM502" s="3"/>
       <c r="AN502" s="3"/>
+      <c r="AO502" s="3"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="3"/>
@@ -21831,6 +22356,7 @@
       <c r="AL503" s="3"/>
       <c r="AM503" s="3"/>
       <c r="AN503" s="3"/>
+      <c r="AO503" s="3"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="3"/>
@@ -21873,6 +22399,7 @@
       <c r="AL504" s="3"/>
       <c r="AM504" s="3"/>
       <c r="AN504" s="3"/>
+      <c r="AO504" s="3"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="3"/>
@@ -21915,6 +22442,7 @@
       <c r="AL505" s="3"/>
       <c r="AM505" s="3"/>
       <c r="AN505" s="3"/>
+      <c r="AO505" s="3"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="3"/>
@@ -21957,6 +22485,7 @@
       <c r="AL506" s="3"/>
       <c r="AM506" s="3"/>
       <c r="AN506" s="3"/>
+      <c r="AO506" s="3"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="3"/>
@@ -21999,6 +22528,7 @@
       <c r="AL507" s="3"/>
       <c r="AM507" s="3"/>
       <c r="AN507" s="3"/>
+      <c r="AO507" s="3"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="3"/>
@@ -22041,6 +22571,7 @@
       <c r="AL508" s="3"/>
       <c r="AM508" s="3"/>
       <c r="AN508" s="3"/>
+      <c r="AO508" s="3"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="3"/>
@@ -22083,6 +22614,7 @@
       <c r="AL509" s="3"/>
       <c r="AM509" s="3"/>
       <c r="AN509" s="3"/>
+      <c r="AO509" s="3"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="3"/>
@@ -22125,6 +22657,7 @@
       <c r="AL510" s="3"/>
       <c r="AM510" s="3"/>
       <c r="AN510" s="3"/>
+      <c r="AO510" s="3"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="3"/>
@@ -22167,6 +22700,7 @@
       <c r="AL511" s="3"/>
       <c r="AM511" s="3"/>
       <c r="AN511" s="3"/>
+      <c r="AO511" s="3"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="3"/>
@@ -22209,6 +22743,7 @@
       <c r="AL512" s="3"/>
       <c r="AM512" s="3"/>
       <c r="AN512" s="3"/>
+      <c r="AO512" s="3"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="3"/>
@@ -22251,6 +22786,7 @@
       <c r="AL513" s="3"/>
       <c r="AM513" s="3"/>
       <c r="AN513" s="3"/>
+      <c r="AO513" s="3"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="3"/>
@@ -22293,6 +22829,7 @@
       <c r="AL514" s="3"/>
       <c r="AM514" s="3"/>
       <c r="AN514" s="3"/>
+      <c r="AO514" s="3"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="3"/>
@@ -22335,6 +22872,7 @@
       <c r="AL515" s="3"/>
       <c r="AM515" s="3"/>
       <c r="AN515" s="3"/>
+      <c r="AO515" s="3"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="3"/>
@@ -22377,6 +22915,7 @@
       <c r="AL516" s="3"/>
       <c r="AM516" s="3"/>
       <c r="AN516" s="3"/>
+      <c r="AO516" s="3"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="3"/>
@@ -22419,6 +22958,7 @@
       <c r="AL517" s="3"/>
       <c r="AM517" s="3"/>
       <c r="AN517" s="3"/>
+      <c r="AO517" s="3"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="3"/>
@@ -22461,6 +23001,7 @@
       <c r="AL518" s="3"/>
       <c r="AM518" s="3"/>
       <c r="AN518" s="3"/>
+      <c r="AO518" s="3"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="3"/>
@@ -22503,6 +23044,7 @@
       <c r="AL519" s="3"/>
       <c r="AM519" s="3"/>
       <c r="AN519" s="3"/>
+      <c r="AO519" s="3"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="3"/>
@@ -22545,6 +23087,7 @@
       <c r="AL520" s="3"/>
       <c r="AM520" s="3"/>
       <c r="AN520" s="3"/>
+      <c r="AO520" s="3"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="3"/>
@@ -22587,6 +23130,7 @@
       <c r="AL521" s="3"/>
       <c r="AM521" s="3"/>
       <c r="AN521" s="3"/>
+      <c r="AO521" s="3"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="3"/>
@@ -22629,6 +23173,7 @@
       <c r="AL522" s="3"/>
       <c r="AM522" s="3"/>
       <c r="AN522" s="3"/>
+      <c r="AO522" s="3"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="3"/>
@@ -22671,6 +23216,7 @@
       <c r="AL523" s="3"/>
       <c r="AM523" s="3"/>
       <c r="AN523" s="3"/>
+      <c r="AO523" s="3"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="3"/>
@@ -22713,6 +23259,7 @@
       <c r="AL524" s="3"/>
       <c r="AM524" s="3"/>
       <c r="AN524" s="3"/>
+      <c r="AO524" s="3"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="3"/>
@@ -22755,6 +23302,7 @@
       <c r="AL525" s="3"/>
       <c r="AM525" s="3"/>
       <c r="AN525" s="3"/>
+      <c r="AO525" s="3"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="3"/>
@@ -22797,6 +23345,7 @@
       <c r="AL526" s="3"/>
       <c r="AM526" s="3"/>
       <c r="AN526" s="3"/>
+      <c r="AO526" s="3"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="3"/>
@@ -22839,6 +23388,7 @@
       <c r="AL527" s="3"/>
       <c r="AM527" s="3"/>
       <c r="AN527" s="3"/>
+      <c r="AO527" s="3"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="3"/>
@@ -22881,6 +23431,7 @@
       <c r="AL528" s="3"/>
       <c r="AM528" s="3"/>
       <c r="AN528" s="3"/>
+      <c r="AO528" s="3"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="3"/>
@@ -22923,6 +23474,7 @@
       <c r="AL529" s="3"/>
       <c r="AM529" s="3"/>
       <c r="AN529" s="3"/>
+      <c r="AO529" s="3"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="3"/>
@@ -22965,6 +23517,7 @@
       <c r="AL530" s="3"/>
       <c r="AM530" s="3"/>
       <c r="AN530" s="3"/>
+      <c r="AO530" s="3"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="3"/>
@@ -23007,6 +23560,7 @@
       <c r="AL531" s="3"/>
       <c r="AM531" s="3"/>
       <c r="AN531" s="3"/>
+      <c r="AO531" s="3"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="3"/>
@@ -23049,6 +23603,7 @@
       <c r="AL532" s="3"/>
       <c r="AM532" s="3"/>
       <c r="AN532" s="3"/>
+      <c r="AO532" s="3"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="3"/>
@@ -23091,6 +23646,7 @@
       <c r="AL533" s="3"/>
       <c r="AM533" s="3"/>
       <c r="AN533" s="3"/>
+      <c r="AO533" s="3"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="3"/>
@@ -23133,6 +23689,7 @@
       <c r="AL534" s="3"/>
       <c r="AM534" s="3"/>
       <c r="AN534" s="3"/>
+      <c r="AO534" s="3"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="3"/>
@@ -23175,6 +23732,7 @@
       <c r="AL535" s="3"/>
       <c r="AM535" s="3"/>
       <c r="AN535" s="3"/>
+      <c r="AO535" s="3"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="3"/>
@@ -23217,6 +23775,7 @@
       <c r="AL536" s="3"/>
       <c r="AM536" s="3"/>
       <c r="AN536" s="3"/>
+      <c r="AO536" s="3"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="3"/>
@@ -23259,6 +23818,7 @@
       <c r="AL537" s="3"/>
       <c r="AM537" s="3"/>
       <c r="AN537" s="3"/>
+      <c r="AO537" s="3"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="3"/>
@@ -23301,6 +23861,7 @@
       <c r="AL538" s="3"/>
       <c r="AM538" s="3"/>
       <c r="AN538" s="3"/>
+      <c r="AO538" s="3"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="3"/>
@@ -23343,6 +23904,7 @@
       <c r="AL539" s="3"/>
       <c r="AM539" s="3"/>
       <c r="AN539" s="3"/>
+      <c r="AO539" s="3"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="3"/>
@@ -23385,6 +23947,7 @@
       <c r="AL540" s="3"/>
       <c r="AM540" s="3"/>
       <c r="AN540" s="3"/>
+      <c r="AO540" s="3"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="3"/>
@@ -23427,6 +23990,7 @@
       <c r="AL541" s="3"/>
       <c r="AM541" s="3"/>
       <c r="AN541" s="3"/>
+      <c r="AO541" s="3"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="3"/>
@@ -23469,6 +24033,7 @@
       <c r="AL542" s="3"/>
       <c r="AM542" s="3"/>
       <c r="AN542" s="3"/>
+      <c r="AO542" s="3"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="3"/>
@@ -23511,6 +24076,7 @@
       <c r="AL543" s="3"/>
       <c r="AM543" s="3"/>
       <c r="AN543" s="3"/>
+      <c r="AO543" s="3"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="3"/>
@@ -23553,6 +24119,7 @@
       <c r="AL544" s="3"/>
       <c r="AM544" s="3"/>
       <c r="AN544" s="3"/>
+      <c r="AO544" s="3"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="3"/>
@@ -23595,6 +24162,7 @@
       <c r="AL545" s="3"/>
       <c r="AM545" s="3"/>
       <c r="AN545" s="3"/>
+      <c r="AO545" s="3"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="3"/>
@@ -23637,6 +24205,7 @@
       <c r="AL546" s="3"/>
       <c r="AM546" s="3"/>
       <c r="AN546" s="3"/>
+      <c r="AO546" s="3"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="3"/>
@@ -23679,6 +24248,7 @@
       <c r="AL547" s="3"/>
       <c r="AM547" s="3"/>
       <c r="AN547" s="3"/>
+      <c r="AO547" s="3"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="3"/>
@@ -23721,6 +24291,7 @@
       <c r="AL548" s="3"/>
       <c r="AM548" s="3"/>
       <c r="AN548" s="3"/>
+      <c r="AO548" s="3"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="3"/>
@@ -23763,6 +24334,7 @@
       <c r="AL549" s="3"/>
       <c r="AM549" s="3"/>
       <c r="AN549" s="3"/>
+      <c r="AO549" s="3"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="3"/>
@@ -23805,6 +24377,7 @@
       <c r="AL550" s="3"/>
       <c r="AM550" s="3"/>
       <c r="AN550" s="3"/>
+      <c r="AO550" s="3"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="3"/>
@@ -23847,6 +24420,7 @@
       <c r="AL551" s="3"/>
       <c r="AM551" s="3"/>
       <c r="AN551" s="3"/>
+      <c r="AO551" s="3"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="3"/>
@@ -23889,6 +24463,7 @@
       <c r="AL552" s="3"/>
       <c r="AM552" s="3"/>
       <c r="AN552" s="3"/>
+      <c r="AO552" s="3"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="3"/>
@@ -23931,6 +24506,7 @@
       <c r="AL553" s="3"/>
       <c r="AM553" s="3"/>
       <c r="AN553" s="3"/>
+      <c r="AO553" s="3"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="3"/>
@@ -23973,6 +24549,7 @@
       <c r="AL554" s="3"/>
       <c r="AM554" s="3"/>
       <c r="AN554" s="3"/>
+      <c r="AO554" s="3"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="3"/>
@@ -24015,6 +24592,7 @@
       <c r="AL555" s="3"/>
       <c r="AM555" s="3"/>
       <c r="AN555" s="3"/>
+      <c r="AO555" s="3"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="3"/>
@@ -24057,6 +24635,7 @@
       <c r="AL556" s="3"/>
       <c r="AM556" s="3"/>
       <c r="AN556" s="3"/>
+      <c r="AO556" s="3"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="3"/>
@@ -24099,6 +24678,7 @@
       <c r="AL557" s="3"/>
       <c r="AM557" s="3"/>
       <c r="AN557" s="3"/>
+      <c r="AO557" s="3"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="3"/>
@@ -24141,6 +24721,7 @@
       <c r="AL558" s="3"/>
       <c r="AM558" s="3"/>
       <c r="AN558" s="3"/>
+      <c r="AO558" s="3"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="3"/>
@@ -24183,6 +24764,7 @@
       <c r="AL559" s="3"/>
       <c r="AM559" s="3"/>
       <c r="AN559" s="3"/>
+      <c r="AO559" s="3"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="3"/>
@@ -24225,6 +24807,7 @@
       <c r="AL560" s="3"/>
       <c r="AM560" s="3"/>
       <c r="AN560" s="3"/>
+      <c r="AO560" s="3"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="3"/>
@@ -24267,6 +24850,7 @@
       <c r="AL561" s="3"/>
       <c r="AM561" s="3"/>
       <c r="AN561" s="3"/>
+      <c r="AO561" s="3"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="3"/>
@@ -24309,6 +24893,7 @@
       <c r="AL562" s="3"/>
       <c r="AM562" s="3"/>
       <c r="AN562" s="3"/>
+      <c r="AO562" s="3"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="3"/>
@@ -24351,6 +24936,7 @@
       <c r="AL563" s="3"/>
       <c r="AM563" s="3"/>
       <c r="AN563" s="3"/>
+      <c r="AO563" s="3"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="3"/>
@@ -24393,6 +24979,7 @@
       <c r="AL564" s="3"/>
       <c r="AM564" s="3"/>
       <c r="AN564" s="3"/>
+      <c r="AO564" s="3"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="3"/>
@@ -24435,6 +25022,7 @@
       <c r="AL565" s="3"/>
       <c r="AM565" s="3"/>
       <c r="AN565" s="3"/>
+      <c r="AO565" s="3"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="3"/>
@@ -24477,6 +25065,7 @@
       <c r="AL566" s="3"/>
       <c r="AM566" s="3"/>
       <c r="AN566" s="3"/>
+      <c r="AO566" s="3"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="3"/>
@@ -24519,6 +25108,7 @@
       <c r="AL567" s="3"/>
       <c r="AM567" s="3"/>
       <c r="AN567" s="3"/>
+      <c r="AO567" s="3"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="3"/>
@@ -24561,6 +25151,7 @@
       <c r="AL568" s="3"/>
       <c r="AM568" s="3"/>
       <c r="AN568" s="3"/>
+      <c r="AO568" s="3"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="3"/>
@@ -24603,6 +25194,7 @@
       <c r="AL569" s="3"/>
       <c r="AM569" s="3"/>
       <c r="AN569" s="3"/>
+      <c r="AO569" s="3"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="3"/>
@@ -24645,6 +25237,7 @@
       <c r="AL570" s="3"/>
       <c r="AM570" s="3"/>
       <c r="AN570" s="3"/>
+      <c r="AO570" s="3"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="3"/>
@@ -24687,6 +25280,7 @@
       <c r="AL571" s="3"/>
       <c r="AM571" s="3"/>
       <c r="AN571" s="3"/>
+      <c r="AO571" s="3"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="3"/>
@@ -24729,6 +25323,7 @@
       <c r="AL572" s="3"/>
       <c r="AM572" s="3"/>
       <c r="AN572" s="3"/>
+      <c r="AO572" s="3"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="3"/>
@@ -24771,6 +25366,7 @@
       <c r="AL573" s="3"/>
       <c r="AM573" s="3"/>
       <c r="AN573" s="3"/>
+      <c r="AO573" s="3"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="3"/>
@@ -24813,6 +25409,7 @@
       <c r="AL574" s="3"/>
       <c r="AM574" s="3"/>
       <c r="AN574" s="3"/>
+      <c r="AO574" s="3"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="3"/>
@@ -24855,6 +25452,7 @@
       <c r="AL575" s="3"/>
       <c r="AM575" s="3"/>
       <c r="AN575" s="3"/>
+      <c r="AO575" s="3"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="3"/>
@@ -24897,6 +25495,7 @@
       <c r="AL576" s="3"/>
       <c r="AM576" s="3"/>
       <c r="AN576" s="3"/>
+      <c r="AO576" s="3"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="3"/>
@@ -24939,6 +25538,7 @@
       <c r="AL577" s="3"/>
       <c r="AM577" s="3"/>
       <c r="AN577" s="3"/>
+      <c r="AO577" s="3"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="3"/>
@@ -24981,6 +25581,7 @@
       <c r="AL578" s="3"/>
       <c r="AM578" s="3"/>
       <c r="AN578" s="3"/>
+      <c r="AO578" s="3"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="3"/>
@@ -25023,6 +25624,7 @@
       <c r="AL579" s="3"/>
       <c r="AM579" s="3"/>
       <c r="AN579" s="3"/>
+      <c r="AO579" s="3"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="3"/>
@@ -25065,6 +25667,7 @@
       <c r="AL580" s="3"/>
       <c r="AM580" s="3"/>
       <c r="AN580" s="3"/>
+      <c r="AO580" s="3"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="3"/>
@@ -25107,6 +25710,7 @@
       <c r="AL581" s="3"/>
       <c r="AM581" s="3"/>
       <c r="AN581" s="3"/>
+      <c r="AO581" s="3"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="3"/>
@@ -25149,6 +25753,7 @@
       <c r="AL582" s="3"/>
       <c r="AM582" s="3"/>
       <c r="AN582" s="3"/>
+      <c r="AO582" s="3"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="3"/>
@@ -25191,6 +25796,7 @@
       <c r="AL583" s="3"/>
       <c r="AM583" s="3"/>
       <c r="AN583" s="3"/>
+      <c r="AO583" s="3"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="3"/>
@@ -25233,6 +25839,7 @@
       <c r="AL584" s="3"/>
       <c r="AM584" s="3"/>
       <c r="AN584" s="3"/>
+      <c r="AO584" s="3"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="3"/>
@@ -25275,6 +25882,7 @@
       <c r="AL585" s="3"/>
       <c r="AM585" s="3"/>
       <c r="AN585" s="3"/>
+      <c r="AO585" s="3"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="3"/>
@@ -25317,6 +25925,7 @@
       <c r="AL586" s="3"/>
       <c r="AM586" s="3"/>
       <c r="AN586" s="3"/>
+      <c r="AO586" s="3"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="3"/>
@@ -25359,6 +25968,7 @@
       <c r="AL587" s="3"/>
       <c r="AM587" s="3"/>
       <c r="AN587" s="3"/>
+      <c r="AO587" s="3"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="3"/>
@@ -25401,6 +26011,7 @@
       <c r="AL588" s="3"/>
       <c r="AM588" s="3"/>
       <c r="AN588" s="3"/>
+      <c r="AO588" s="3"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="3"/>
@@ -25443,6 +26054,7 @@
       <c r="AL589" s="3"/>
       <c r="AM589" s="3"/>
       <c r="AN589" s="3"/>
+      <c r="AO589" s="3"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="3"/>
@@ -25485,6 +26097,7 @@
       <c r="AL590" s="3"/>
       <c r="AM590" s="3"/>
       <c r="AN590" s="3"/>
+      <c r="AO590" s="3"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="3"/>
@@ -25527,6 +26140,7 @@
       <c r="AL591" s="3"/>
       <c r="AM591" s="3"/>
       <c r="AN591" s="3"/>
+      <c r="AO591" s="3"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="3"/>
@@ -25569,6 +26183,7 @@
       <c r="AL592" s="3"/>
       <c r="AM592" s="3"/>
       <c r="AN592" s="3"/>
+      <c r="AO592" s="3"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="3"/>
@@ -25611,6 +26226,7 @@
       <c r="AL593" s="3"/>
       <c r="AM593" s="3"/>
       <c r="AN593" s="3"/>
+      <c r="AO593" s="3"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="3"/>
@@ -25653,6 +26269,7 @@
       <c r="AL594" s="3"/>
       <c r="AM594" s="3"/>
       <c r="AN594" s="3"/>
+      <c r="AO594" s="3"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="3"/>
@@ -25695,6 +26312,7 @@
       <c r="AL595" s="3"/>
       <c r="AM595" s="3"/>
       <c r="AN595" s="3"/>
+      <c r="AO595" s="3"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="3"/>
@@ -25737,6 +26355,7 @@
       <c r="AL596" s="3"/>
       <c r="AM596" s="3"/>
       <c r="AN596" s="3"/>
+      <c r="AO596" s="3"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="3"/>
@@ -25779,6 +26398,7 @@
       <c r="AL597" s="3"/>
       <c r="AM597" s="3"/>
       <c r="AN597" s="3"/>
+      <c r="AO597" s="3"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="3"/>
@@ -25821,6 +26441,7 @@
       <c r="AL598" s="3"/>
       <c r="AM598" s="3"/>
       <c r="AN598" s="3"/>
+      <c r="AO598" s="3"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="3"/>
@@ -25863,6 +26484,7 @@
       <c r="AL599" s="3"/>
       <c r="AM599" s="3"/>
       <c r="AN599" s="3"/>
+      <c r="AO599" s="3"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="3"/>
@@ -25905,6 +26527,7 @@
       <c r="AL600" s="3"/>
       <c r="AM600" s="3"/>
       <c r="AN600" s="3"/>
+      <c r="AO600" s="3"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="3"/>
@@ -25947,6 +26570,7 @@
       <c r="AL601" s="3"/>
       <c r="AM601" s="3"/>
       <c r="AN601" s="3"/>
+      <c r="AO601" s="3"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="3"/>
@@ -25989,6 +26613,7 @@
       <c r="AL602" s="3"/>
       <c r="AM602" s="3"/>
       <c r="AN602" s="3"/>
+      <c r="AO602" s="3"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="3"/>
@@ -26031,6 +26656,7 @@
       <c r="AL603" s="3"/>
       <c r="AM603" s="3"/>
       <c r="AN603" s="3"/>
+      <c r="AO603" s="3"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="3"/>
@@ -26073,6 +26699,7 @@
       <c r="AL604" s="3"/>
       <c r="AM604" s="3"/>
       <c r="AN604" s="3"/>
+      <c r="AO604" s="3"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="3"/>
@@ -26115,6 +26742,7 @@
       <c r="AL605" s="3"/>
       <c r="AM605" s="3"/>
       <c r="AN605" s="3"/>
+      <c r="AO605" s="3"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="3"/>
@@ -26157,6 +26785,7 @@
       <c r="AL606" s="3"/>
       <c r="AM606" s="3"/>
       <c r="AN606" s="3"/>
+      <c r="AO606" s="3"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="3"/>
@@ -26199,6 +26828,7 @@
       <c r="AL607" s="3"/>
       <c r="AM607" s="3"/>
       <c r="AN607" s="3"/>
+      <c r="AO607" s="3"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="3"/>
@@ -26241,6 +26871,7 @@
       <c r="AL608" s="3"/>
       <c r="AM608" s="3"/>
       <c r="AN608" s="3"/>
+      <c r="AO608" s="3"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="3"/>
@@ -26283,6 +26914,7 @@
       <c r="AL609" s="3"/>
       <c r="AM609" s="3"/>
       <c r="AN609" s="3"/>
+      <c r="AO609" s="3"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="3"/>
@@ -26325,6 +26957,7 @@
       <c r="AL610" s="3"/>
       <c r="AM610" s="3"/>
       <c r="AN610" s="3"/>
+      <c r="AO610" s="3"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="3"/>
@@ -26367,6 +27000,7 @@
       <c r="AL611" s="3"/>
       <c r="AM611" s="3"/>
       <c r="AN611" s="3"/>
+      <c r="AO611" s="3"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="3"/>
@@ -26409,6 +27043,7 @@
       <c r="AL612" s="3"/>
       <c r="AM612" s="3"/>
       <c r="AN612" s="3"/>
+      <c r="AO612" s="3"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="3"/>
@@ -26451,6 +27086,7 @@
       <c r="AL613" s="3"/>
       <c r="AM613" s="3"/>
       <c r="AN613" s="3"/>
+      <c r="AO613" s="3"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="3"/>
@@ -26493,6 +27129,7 @@
       <c r="AL614" s="3"/>
       <c r="AM614" s="3"/>
       <c r="AN614" s="3"/>
+      <c r="AO614" s="3"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="3"/>
@@ -26535,6 +27172,7 @@
       <c r="AL615" s="3"/>
       <c r="AM615" s="3"/>
       <c r="AN615" s="3"/>
+      <c r="AO615" s="3"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="3"/>
@@ -26577,6 +27215,7 @@
       <c r="AL616" s="3"/>
       <c r="AM616" s="3"/>
       <c r="AN616" s="3"/>
+      <c r="AO616" s="3"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="3"/>
@@ -26619,6 +27258,7 @@
       <c r="AL617" s="3"/>
       <c r="AM617" s="3"/>
       <c r="AN617" s="3"/>
+      <c r="AO617" s="3"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="3"/>
@@ -26661,6 +27301,7 @@
       <c r="AL618" s="3"/>
       <c r="AM618" s="3"/>
       <c r="AN618" s="3"/>
+      <c r="AO618" s="3"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="3"/>
@@ -26703,6 +27344,7 @@
       <c r="AL619" s="3"/>
       <c r="AM619" s="3"/>
       <c r="AN619" s="3"/>
+      <c r="AO619" s="3"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="3"/>
@@ -26745,6 +27387,7 @@
       <c r="AL620" s="3"/>
       <c r="AM620" s="3"/>
       <c r="AN620" s="3"/>
+      <c r="AO620" s="3"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="3"/>
@@ -26787,6 +27430,7 @@
       <c r="AL621" s="3"/>
       <c r="AM621" s="3"/>
       <c r="AN621" s="3"/>
+      <c r="AO621" s="3"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="3"/>
@@ -26829,6 +27473,7 @@
       <c r="AL622" s="3"/>
       <c r="AM622" s="3"/>
       <c r="AN622" s="3"/>
+      <c r="AO622" s="3"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="3"/>
@@ -26871,6 +27516,7 @@
       <c r="AL623" s="3"/>
       <c r="AM623" s="3"/>
       <c r="AN623" s="3"/>
+      <c r="AO623" s="3"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="3"/>
@@ -26913,6 +27559,7 @@
       <c r="AL624" s="3"/>
       <c r="AM624" s="3"/>
       <c r="AN624" s="3"/>
+      <c r="AO624" s="3"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="3"/>
@@ -26955,6 +27602,7 @@
       <c r="AL625" s="3"/>
       <c r="AM625" s="3"/>
       <c r="AN625" s="3"/>
+      <c r="AO625" s="3"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="3"/>
@@ -26997,6 +27645,7 @@
       <c r="AL626" s="3"/>
       <c r="AM626" s="3"/>
       <c r="AN626" s="3"/>
+      <c r="AO626" s="3"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="3"/>
@@ -27039,6 +27688,7 @@
       <c r="AL627" s="3"/>
       <c r="AM627" s="3"/>
       <c r="AN627" s="3"/>
+      <c r="AO627" s="3"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="3"/>
@@ -27081,6 +27731,7 @@
       <c r="AL628" s="3"/>
       <c r="AM628" s="3"/>
       <c r="AN628" s="3"/>
+      <c r="AO628" s="3"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="3"/>
@@ -27123,6 +27774,7 @@
       <c r="AL629" s="3"/>
       <c r="AM629" s="3"/>
       <c r="AN629" s="3"/>
+      <c r="AO629" s="3"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="3"/>
@@ -27165,6 +27817,7 @@
       <c r="AL630" s="3"/>
       <c r="AM630" s="3"/>
       <c r="AN630" s="3"/>
+      <c r="AO630" s="3"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="3"/>
@@ -27207,6 +27860,7 @@
       <c r="AL631" s="3"/>
       <c r="AM631" s="3"/>
       <c r="AN631" s="3"/>
+      <c r="AO631" s="3"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="3"/>
@@ -27249,6 +27903,7 @@
       <c r="AL632" s="3"/>
       <c r="AM632" s="3"/>
       <c r="AN632" s="3"/>
+      <c r="AO632" s="3"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="3"/>
@@ -27291,6 +27946,7 @@
       <c r="AL633" s="3"/>
       <c r="AM633" s="3"/>
       <c r="AN633" s="3"/>
+      <c r="AO633" s="3"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="3"/>
@@ -27333,6 +27989,7 @@
       <c r="AL634" s="3"/>
       <c r="AM634" s="3"/>
       <c r="AN634" s="3"/>
+      <c r="AO634" s="3"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="3"/>
@@ -27375,6 +28032,7 @@
       <c r="AL635" s="3"/>
       <c r="AM635" s="3"/>
       <c r="AN635" s="3"/>
+      <c r="AO635" s="3"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="3"/>
@@ -27417,6 +28075,7 @@
       <c r="AL636" s="3"/>
       <c r="AM636" s="3"/>
       <c r="AN636" s="3"/>
+      <c r="AO636" s="3"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="3"/>
@@ -27459,6 +28118,7 @@
       <c r="AL637" s="3"/>
       <c r="AM637" s="3"/>
       <c r="AN637" s="3"/>
+      <c r="AO637" s="3"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="3"/>
@@ -27501,6 +28161,7 @@
       <c r="AL638" s="3"/>
       <c r="AM638" s="3"/>
       <c r="AN638" s="3"/>
+      <c r="AO638" s="3"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="3"/>
@@ -27543,6 +28204,7 @@
       <c r="AL639" s="3"/>
       <c r="AM639" s="3"/>
       <c r="AN639" s="3"/>
+      <c r="AO639" s="3"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="3"/>
@@ -27585,6 +28247,7 @@
       <c r="AL640" s="3"/>
       <c r="AM640" s="3"/>
       <c r="AN640" s="3"/>
+      <c r="AO640" s="3"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="3"/>
@@ -27627,6 +28290,7 @@
       <c r="AL641" s="3"/>
       <c r="AM641" s="3"/>
       <c r="AN641" s="3"/>
+      <c r="AO641" s="3"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="3"/>
@@ -27669,6 +28333,7 @@
       <c r="AL642" s="3"/>
       <c r="AM642" s="3"/>
       <c r="AN642" s="3"/>
+      <c r="AO642" s="3"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="3"/>
@@ -27711,6 +28376,7 @@
       <c r="AL643" s="3"/>
       <c r="AM643" s="3"/>
       <c r="AN643" s="3"/>
+      <c r="AO643" s="3"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="3"/>
@@ -27753,6 +28419,7 @@
       <c r="AL644" s="3"/>
       <c r="AM644" s="3"/>
       <c r="AN644" s="3"/>
+      <c r="AO644" s="3"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="3"/>
@@ -27795,6 +28462,7 @@
       <c r="AL645" s="3"/>
       <c r="AM645" s="3"/>
       <c r="AN645" s="3"/>
+      <c r="AO645" s="3"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="3"/>
@@ -27837,6 +28505,7 @@
       <c r="AL646" s="3"/>
       <c r="AM646" s="3"/>
       <c r="AN646" s="3"/>
+      <c r="AO646" s="3"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="3"/>
@@ -27879,6 +28548,7 @@
       <c r="AL647" s="3"/>
       <c r="AM647" s="3"/>
       <c r="AN647" s="3"/>
+      <c r="AO647" s="3"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="3"/>
@@ -27921,6 +28591,7 @@
       <c r="AL648" s="3"/>
       <c r="AM648" s="3"/>
       <c r="AN648" s="3"/>
+      <c r="AO648" s="3"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="3"/>
@@ -27963,6 +28634,7 @@
       <c r="AL649" s="3"/>
       <c r="AM649" s="3"/>
       <c r="AN649" s="3"/>
+      <c r="AO649" s="3"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="3"/>
@@ -28005,6 +28677,7 @@
       <c r="AL650" s="3"/>
       <c r="AM650" s="3"/>
       <c r="AN650" s="3"/>
+      <c r="AO650" s="3"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="3"/>
@@ -28047,6 +28720,7 @@
       <c r="AL651" s="3"/>
       <c r="AM651" s="3"/>
       <c r="AN651" s="3"/>
+      <c r="AO651" s="3"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="3"/>
@@ -28089,6 +28763,7 @@
       <c r="AL652" s="3"/>
       <c r="AM652" s="3"/>
       <c r="AN652" s="3"/>
+      <c r="AO652" s="3"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="3"/>
@@ -28131,6 +28806,7 @@
       <c r="AL653" s="3"/>
       <c r="AM653" s="3"/>
       <c r="AN653" s="3"/>
+      <c r="AO653" s="3"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="3"/>
@@ -28173,6 +28849,7 @@
       <c r="AL654" s="3"/>
       <c r="AM654" s="3"/>
       <c r="AN654" s="3"/>
+      <c r="AO654" s="3"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="3"/>
@@ -28215,6 +28892,7 @@
       <c r="AL655" s="3"/>
       <c r="AM655" s="3"/>
       <c r="AN655" s="3"/>
+      <c r="AO655" s="3"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="3"/>
@@ -28257,6 +28935,7 @@
       <c r="AL656" s="3"/>
       <c r="AM656" s="3"/>
       <c r="AN656" s="3"/>
+      <c r="AO656" s="3"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="3"/>
@@ -28299,6 +28978,7 @@
       <c r="AL657" s="3"/>
       <c r="AM657" s="3"/>
       <c r="AN657" s="3"/>
+      <c r="AO657" s="3"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="3"/>
@@ -28341,6 +29021,7 @@
       <c r="AL658" s="3"/>
       <c r="AM658" s="3"/>
       <c r="AN658" s="3"/>
+      <c r="AO658" s="3"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="3"/>
@@ -28383,6 +29064,7 @@
       <c r="AL659" s="3"/>
       <c r="AM659" s="3"/>
       <c r="AN659" s="3"/>
+      <c r="AO659" s="3"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="3"/>
@@ -28425,6 +29107,7 @@
       <c r="AL660" s="3"/>
       <c r="AM660" s="3"/>
       <c r="AN660" s="3"/>
+      <c r="AO660" s="3"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="3"/>
@@ -28467,6 +29150,7 @@
       <c r="AL661" s="3"/>
       <c r="AM661" s="3"/>
       <c r="AN661" s="3"/>
+      <c r="AO661" s="3"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="3"/>
@@ -28509,6 +29193,7 @@
       <c r="AL662" s="3"/>
       <c r="AM662" s="3"/>
       <c r="AN662" s="3"/>
+      <c r="AO662" s="3"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="3"/>
@@ -28551,6 +29236,7 @@
       <c r="AL663" s="3"/>
       <c r="AM663" s="3"/>
       <c r="AN663" s="3"/>
+      <c r="AO663" s="3"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="3"/>
@@ -28593,6 +29279,7 @@
       <c r="AL664" s="3"/>
       <c r="AM664" s="3"/>
       <c r="AN664" s="3"/>
+      <c r="AO664" s="3"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="3"/>
@@ -28635,6 +29322,7 @@
       <c r="AL665" s="3"/>
       <c r="AM665" s="3"/>
       <c r="AN665" s="3"/>
+      <c r="AO665" s="3"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="3"/>
@@ -28677,6 +29365,7 @@
       <c r="AL666" s="3"/>
       <c r="AM666" s="3"/>
       <c r="AN666" s="3"/>
+      <c r="AO666" s="3"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="3"/>
@@ -28719,6 +29408,7 @@
       <c r="AL667" s="3"/>
       <c r="AM667" s="3"/>
       <c r="AN667" s="3"/>
+      <c r="AO667" s="3"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="3"/>
@@ -28761,6 +29451,7 @@
       <c r="AL668" s="3"/>
       <c r="AM668" s="3"/>
       <c r="AN668" s="3"/>
+      <c r="AO668" s="3"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="3"/>
@@ -28803,6 +29494,7 @@
       <c r="AL669" s="3"/>
       <c r="AM669" s="3"/>
       <c r="AN669" s="3"/>
+      <c r="AO669" s="3"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="3"/>
@@ -28845,6 +29537,7 @@
       <c r="AL670" s="3"/>
       <c r="AM670" s="3"/>
       <c r="AN670" s="3"/>
+      <c r="AO670" s="3"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="3"/>
@@ -28887,6 +29580,7 @@
       <c r="AL671" s="3"/>
       <c r="AM671" s="3"/>
       <c r="AN671" s="3"/>
+      <c r="AO671" s="3"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="3"/>
@@ -28929,6 +29623,7 @@
       <c r="AL672" s="3"/>
       <c r="AM672" s="3"/>
       <c r="AN672" s="3"/>
+      <c r="AO672" s="3"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="3"/>
@@ -28971,6 +29666,7 @@
       <c r="AL673" s="3"/>
       <c r="AM673" s="3"/>
       <c r="AN673" s="3"/>
+      <c r="AO673" s="3"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="3"/>
@@ -29013,6 +29709,7 @@
       <c r="AL674" s="3"/>
       <c r="AM674" s="3"/>
       <c r="AN674" s="3"/>
+      <c r="AO674" s="3"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="3"/>
@@ -29055,6 +29752,7 @@
       <c r="AL675" s="3"/>
       <c r="AM675" s="3"/>
       <c r="AN675" s="3"/>
+      <c r="AO675" s="3"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="3"/>
@@ -29097,6 +29795,7 @@
       <c r="AL676" s="3"/>
       <c r="AM676" s="3"/>
       <c r="AN676" s="3"/>
+      <c r="AO676" s="3"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="3"/>
@@ -29139,6 +29838,7 @@
       <c r="AL677" s="3"/>
       <c r="AM677" s="3"/>
       <c r="AN677" s="3"/>
+      <c r="AO677" s="3"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="3"/>
@@ -29181,6 +29881,7 @@
       <c r="AL678" s="3"/>
       <c r="AM678" s="3"/>
       <c r="AN678" s="3"/>
+      <c r="AO678" s="3"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="3"/>
@@ -29223,6 +29924,7 @@
       <c r="AL679" s="3"/>
       <c r="AM679" s="3"/>
       <c r="AN679" s="3"/>
+      <c r="AO679" s="3"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="3"/>
@@ -29265,6 +29967,7 @@
       <c r="AL680" s="3"/>
       <c r="AM680" s="3"/>
       <c r="AN680" s="3"/>
+      <c r="AO680" s="3"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="3"/>
@@ -29307,6 +30010,7 @@
       <c r="AL681" s="3"/>
       <c r="AM681" s="3"/>
       <c r="AN681" s="3"/>
+      <c r="AO681" s="3"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="3"/>
@@ -29349,6 +30053,7 @@
       <c r="AL682" s="3"/>
       <c r="AM682" s="3"/>
       <c r="AN682" s="3"/>
+      <c r="AO682" s="3"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="3"/>
@@ -29391,6 +30096,7 @@
       <c r="AL683" s="3"/>
       <c r="AM683" s="3"/>
       <c r="AN683" s="3"/>
+      <c r="AO683" s="3"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="3"/>
@@ -29433,6 +30139,7 @@
       <c r="AL684" s="3"/>
       <c r="AM684" s="3"/>
       <c r="AN684" s="3"/>
+      <c r="AO684" s="3"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="3"/>
@@ -29475,6 +30182,7 @@
       <c r="AL685" s="3"/>
       <c r="AM685" s="3"/>
       <c r="AN685" s="3"/>
+      <c r="AO685" s="3"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="3"/>
@@ -29517,6 +30225,7 @@
       <c r="AL686" s="3"/>
       <c r="AM686" s="3"/>
       <c r="AN686" s="3"/>
+      <c r="AO686" s="3"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="3"/>
@@ -29559,6 +30268,7 @@
       <c r="AL687" s="3"/>
       <c r="AM687" s="3"/>
       <c r="AN687" s="3"/>
+      <c r="AO687" s="3"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="3"/>
@@ -29601,6 +30311,7 @@
       <c r="AL688" s="3"/>
       <c r="AM688" s="3"/>
       <c r="AN688" s="3"/>
+      <c r="AO688" s="3"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="3"/>
@@ -29643,6 +30354,7 @@
       <c r="AL689" s="3"/>
       <c r="AM689" s="3"/>
       <c r="AN689" s="3"/>
+      <c r="AO689" s="3"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="3"/>
@@ -29685,6 +30397,7 @@
       <c r="AL690" s="3"/>
       <c r="AM690" s="3"/>
       <c r="AN690" s="3"/>
+      <c r="AO690" s="3"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="3"/>
@@ -29727,6 +30440,7 @@
       <c r="AL691" s="3"/>
       <c r="AM691" s="3"/>
       <c r="AN691" s="3"/>
+      <c r="AO691" s="3"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="3"/>
@@ -29769,6 +30483,7 @@
       <c r="AL692" s="3"/>
       <c r="AM692" s="3"/>
       <c r="AN692" s="3"/>
+      <c r="AO692" s="3"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="3"/>
@@ -29811,6 +30526,7 @@
       <c r="AL693" s="3"/>
       <c r="AM693" s="3"/>
       <c r="AN693" s="3"/>
+      <c r="AO693" s="3"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="3"/>
@@ -29853,6 +30569,7 @@
       <c r="AL694" s="3"/>
       <c r="AM694" s="3"/>
       <c r="AN694" s="3"/>
+      <c r="AO694" s="3"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="3"/>
@@ -29895,6 +30612,7 @@
       <c r="AL695" s="3"/>
       <c r="AM695" s="3"/>
       <c r="AN695" s="3"/>
+      <c r="AO695" s="3"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="3"/>
@@ -29937,6 +30655,7 @@
       <c r="AL696" s="3"/>
       <c r="AM696" s="3"/>
       <c r="AN696" s="3"/>
+      <c r="AO696" s="3"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="3"/>
@@ -29979,6 +30698,7 @@
       <c r="AL697" s="3"/>
       <c r="AM697" s="3"/>
       <c r="AN697" s="3"/>
+      <c r="AO697" s="3"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="3"/>
@@ -30021,6 +30741,7 @@
       <c r="AL698" s="3"/>
       <c r="AM698" s="3"/>
       <c r="AN698" s="3"/>
+      <c r="AO698" s="3"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="3"/>
@@ -30063,6 +30784,7 @@
       <c r="AL699" s="3"/>
       <c r="AM699" s="3"/>
       <c r="AN699" s="3"/>
+      <c r="AO699" s="3"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="3"/>
@@ -30105,6 +30827,7 @@
       <c r="AL700" s="3"/>
       <c r="AM700" s="3"/>
       <c r="AN700" s="3"/>
+      <c r="AO700" s="3"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="3"/>
@@ -30147,6 +30870,7 @@
       <c r="AL701" s="3"/>
       <c r="AM701" s="3"/>
       <c r="AN701" s="3"/>
+      <c r="AO701" s="3"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="3"/>
@@ -30189,6 +30913,7 @@
       <c r="AL702" s="3"/>
       <c r="AM702" s="3"/>
       <c r="AN702" s="3"/>
+      <c r="AO702" s="3"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="3"/>
@@ -30231,6 +30956,7 @@
       <c r="AL703" s="3"/>
       <c r="AM703" s="3"/>
       <c r="AN703" s="3"/>
+      <c r="AO703" s="3"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="3"/>
@@ -30273,6 +30999,7 @@
       <c r="AL704" s="3"/>
       <c r="AM704" s="3"/>
       <c r="AN704" s="3"/>
+      <c r="AO704" s="3"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="3"/>
@@ -30315,6 +31042,7 @@
       <c r="AL705" s="3"/>
       <c r="AM705" s="3"/>
       <c r="AN705" s="3"/>
+      <c r="AO705" s="3"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="3"/>
@@ -30357,6 +31085,7 @@
       <c r="AL706" s="3"/>
       <c r="AM706" s="3"/>
       <c r="AN706" s="3"/>
+      <c r="AO706" s="3"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="3"/>
@@ -30399,6 +31128,7 @@
       <c r="AL707" s="3"/>
       <c r="AM707" s="3"/>
       <c r="AN707" s="3"/>
+      <c r="AO707" s="3"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="3"/>
@@ -30441,6 +31171,7 @@
       <c r="AL708" s="3"/>
       <c r="AM708" s="3"/>
       <c r="AN708" s="3"/>
+      <c r="AO708" s="3"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="3"/>
@@ -30483,6 +31214,7 @@
       <c r="AL709" s="3"/>
       <c r="AM709" s="3"/>
       <c r="AN709" s="3"/>
+      <c r="AO709" s="3"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="3"/>
@@ -30525,6 +31257,7 @@
       <c r="AL710" s="3"/>
       <c r="AM710" s="3"/>
       <c r="AN710" s="3"/>
+      <c r="AO710" s="3"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="3"/>
@@ -30567,6 +31300,7 @@
       <c r="AL711" s="3"/>
       <c r="AM711" s="3"/>
       <c r="AN711" s="3"/>
+      <c r="AO711" s="3"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="3"/>
@@ -30609,6 +31343,7 @@
       <c r="AL712" s="3"/>
       <c r="AM712" s="3"/>
       <c r="AN712" s="3"/>
+      <c r="AO712" s="3"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="3"/>
@@ -30651,6 +31386,7 @@
       <c r="AL713" s="3"/>
       <c r="AM713" s="3"/>
       <c r="AN713" s="3"/>
+      <c r="AO713" s="3"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="3"/>
@@ -30693,6 +31429,7 @@
       <c r="AL714" s="3"/>
       <c r="AM714" s="3"/>
       <c r="AN714" s="3"/>
+      <c r="AO714" s="3"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="3"/>
@@ -30735,6 +31472,7 @@
       <c r="AL715" s="3"/>
       <c r="AM715" s="3"/>
       <c r="AN715" s="3"/>
+      <c r="AO715" s="3"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="3"/>
@@ -30777,6 +31515,7 @@
       <c r="AL716" s="3"/>
       <c r="AM716" s="3"/>
       <c r="AN716" s="3"/>
+      <c r="AO716" s="3"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="3"/>
@@ -30819,6 +31558,7 @@
       <c r="AL717" s="3"/>
       <c r="AM717" s="3"/>
       <c r="AN717" s="3"/>
+      <c r="AO717" s="3"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="3"/>
@@ -30861,6 +31601,7 @@
       <c r="AL718" s="3"/>
       <c r="AM718" s="3"/>
       <c r="AN718" s="3"/>
+      <c r="AO718" s="3"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="3"/>
@@ -30903,6 +31644,7 @@
       <c r="AL719" s="3"/>
       <c r="AM719" s="3"/>
       <c r="AN719" s="3"/>
+      <c r="AO719" s="3"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="3"/>
@@ -30945,6 +31687,7 @@
       <c r="AL720" s="3"/>
       <c r="AM720" s="3"/>
       <c r="AN720" s="3"/>
+      <c r="AO720" s="3"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="3"/>
@@ -30987,6 +31730,7 @@
       <c r="AL721" s="3"/>
       <c r="AM721" s="3"/>
       <c r="AN721" s="3"/>
+      <c r="AO721" s="3"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="3"/>
@@ -31029,6 +31773,7 @@
       <c r="AL722" s="3"/>
       <c r="AM722" s="3"/>
       <c r="AN722" s="3"/>
+      <c r="AO722" s="3"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="3"/>
@@ -31071,6 +31816,7 @@
       <c r="AL723" s="3"/>
       <c r="AM723" s="3"/>
       <c r="AN723" s="3"/>
+      <c r="AO723" s="3"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="3"/>
@@ -31113,6 +31859,7 @@
       <c r="AL724" s="3"/>
       <c r="AM724" s="3"/>
       <c r="AN724" s="3"/>
+      <c r="AO724" s="3"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="3"/>
@@ -31155,6 +31902,7 @@
       <c r="AL725" s="3"/>
       <c r="AM725" s="3"/>
       <c r="AN725" s="3"/>
+      <c r="AO725" s="3"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="3"/>
@@ -31197,6 +31945,7 @@
       <c r="AL726" s="3"/>
       <c r="AM726" s="3"/>
       <c r="AN726" s="3"/>
+      <c r="AO726" s="3"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="3"/>
@@ -31239,6 +31988,7 @@
       <c r="AL727" s="3"/>
       <c r="AM727" s="3"/>
       <c r="AN727" s="3"/>
+      <c r="AO727" s="3"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="3"/>
@@ -31281,6 +32031,7 @@
       <c r="AL728" s="3"/>
       <c r="AM728" s="3"/>
       <c r="AN728" s="3"/>
+      <c r="AO728" s="3"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="3"/>
@@ -31323,6 +32074,7 @@
       <c r="AL729" s="3"/>
       <c r="AM729" s="3"/>
       <c r="AN729" s="3"/>
+      <c r="AO729" s="3"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="3"/>
@@ -31365,6 +32117,7 @@
       <c r="AL730" s="3"/>
       <c r="AM730" s="3"/>
       <c r="AN730" s="3"/>
+      <c r="AO730" s="3"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="3"/>
@@ -31407,6 +32160,7 @@
       <c r="AL731" s="3"/>
       <c r="AM731" s="3"/>
       <c r="AN731" s="3"/>
+      <c r="AO731" s="3"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="3"/>
@@ -31449,6 +32203,7 @@
       <c r="AL732" s="3"/>
       <c r="AM732" s="3"/>
       <c r="AN732" s="3"/>
+      <c r="AO732" s="3"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="3"/>
@@ -31491,6 +32246,7 @@
       <c r="AL733" s="3"/>
       <c r="AM733" s="3"/>
       <c r="AN733" s="3"/>
+      <c r="AO733" s="3"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="3"/>
@@ -31533,6 +32289,7 @@
       <c r="AL734" s="3"/>
       <c r="AM734" s="3"/>
       <c r="AN734" s="3"/>
+      <c r="AO734" s="3"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="3"/>
@@ -31575,6 +32332,7 @@
       <c r="AL735" s="3"/>
       <c r="AM735" s="3"/>
       <c r="AN735" s="3"/>
+      <c r="AO735" s="3"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="3"/>
@@ -31617,6 +32375,7 @@
       <c r="AL736" s="3"/>
       <c r="AM736" s="3"/>
       <c r="AN736" s="3"/>
+      <c r="AO736" s="3"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="3"/>
@@ -31659,6 +32418,7 @@
       <c r="AL737" s="3"/>
       <c r="AM737" s="3"/>
       <c r="AN737" s="3"/>
+      <c r="AO737" s="3"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="3"/>
@@ -31701,6 +32461,7 @@
       <c r="AL738" s="3"/>
       <c r="AM738" s="3"/>
       <c r="AN738" s="3"/>
+      <c r="AO738" s="3"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="3"/>
@@ -31743,6 +32504,7 @@
       <c r="AL739" s="3"/>
       <c r="AM739" s="3"/>
       <c r="AN739" s="3"/>
+      <c r="AO739" s="3"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="3"/>
@@ -31785,6 +32547,7 @@
       <c r="AL740" s="3"/>
       <c r="AM740" s="3"/>
       <c r="AN740" s="3"/>
+      <c r="AO740" s="3"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="3"/>
@@ -31827,6 +32590,7 @@
       <c r="AL741" s="3"/>
       <c r="AM741" s="3"/>
       <c r="AN741" s="3"/>
+      <c r="AO741" s="3"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="3"/>
@@ -31869,6 +32633,7 @@
       <c r="AL742" s="3"/>
       <c r="AM742" s="3"/>
       <c r="AN742" s="3"/>
+      <c r="AO742" s="3"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="3"/>
@@ -31911,6 +32676,7 @@
       <c r="AL743" s="3"/>
       <c r="AM743" s="3"/>
       <c r="AN743" s="3"/>
+      <c r="AO743" s="3"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="3"/>
@@ -31953,6 +32719,7 @@
       <c r="AL744" s="3"/>
       <c r="AM744" s="3"/>
       <c r="AN744" s="3"/>
+      <c r="AO744" s="3"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="3"/>
@@ -31995,6 +32762,7 @@
       <c r="AL745" s="3"/>
       <c r="AM745" s="3"/>
       <c r="AN745" s="3"/>
+      <c r="AO745" s="3"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="3"/>
@@ -32037,6 +32805,7 @@
       <c r="AL746" s="3"/>
       <c r="AM746" s="3"/>
       <c r="AN746" s="3"/>
+      <c r="AO746" s="3"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="3"/>
@@ -32079,6 +32848,7 @@
       <c r="AL747" s="3"/>
       <c r="AM747" s="3"/>
       <c r="AN747" s="3"/>
+      <c r="AO747" s="3"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="3"/>
@@ -32121,6 +32891,7 @@
       <c r="AL748" s="3"/>
       <c r="AM748" s="3"/>
       <c r="AN748" s="3"/>
+      <c r="AO748" s="3"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="3"/>
@@ -32163,6 +32934,7 @@
       <c r="AL749" s="3"/>
       <c r="AM749" s="3"/>
       <c r="AN749" s="3"/>
+      <c r="AO749" s="3"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="3"/>
@@ -32205,6 +32977,7 @@
       <c r="AL750" s="3"/>
       <c r="AM750" s="3"/>
       <c r="AN750" s="3"/>
+      <c r="AO750" s="3"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="3"/>
@@ -32247,6 +33020,7 @@
       <c r="AL751" s="3"/>
       <c r="AM751" s="3"/>
       <c r="AN751" s="3"/>
+      <c r="AO751" s="3"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="3"/>
@@ -32289,6 +33063,7 @@
       <c r="AL752" s="3"/>
       <c r="AM752" s="3"/>
       <c r="AN752" s="3"/>
+      <c r="AO752" s="3"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="3"/>
@@ -32331,6 +33106,7 @@
       <c r="AL753" s="3"/>
       <c r="AM753" s="3"/>
       <c r="AN753" s="3"/>
+      <c r="AO753" s="3"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="3"/>
@@ -32373,6 +33149,7 @@
       <c r="AL754" s="3"/>
       <c r="AM754" s="3"/>
       <c r="AN754" s="3"/>
+      <c r="AO754" s="3"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="3"/>
@@ -32415,6 +33192,7 @@
       <c r="AL755" s="3"/>
       <c r="AM755" s="3"/>
       <c r="AN755" s="3"/>
+      <c r="AO755" s="3"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="3"/>
@@ -32457,6 +33235,7 @@
       <c r="AL756" s="3"/>
       <c r="AM756" s="3"/>
       <c r="AN756" s="3"/>
+      <c r="AO756" s="3"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="3"/>
@@ -32499,6 +33278,7 @@
       <c r="AL757" s="3"/>
       <c r="AM757" s="3"/>
       <c r="AN757" s="3"/>
+      <c r="AO757" s="3"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="3"/>
@@ -32541,6 +33321,7 @@
       <c r="AL758" s="3"/>
       <c r="AM758" s="3"/>
       <c r="AN758" s="3"/>
+      <c r="AO758" s="3"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="3"/>
@@ -32583,6 +33364,7 @@
       <c r="AL759" s="3"/>
       <c r="AM759" s="3"/>
       <c r="AN759" s="3"/>
+      <c r="AO759" s="3"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="3"/>
@@ -32625,6 +33407,7 @@
       <c r="AL760" s="3"/>
       <c r="AM760" s="3"/>
       <c r="AN760" s="3"/>
+      <c r="AO760" s="3"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="3"/>
@@ -32667,6 +33450,7 @@
       <c r="AL761" s="3"/>
       <c r="AM761" s="3"/>
       <c r="AN761" s="3"/>
+      <c r="AO761" s="3"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="3"/>
@@ -32709,6 +33493,7 @@
       <c r="AL762" s="3"/>
       <c r="AM762" s="3"/>
       <c r="AN762" s="3"/>
+      <c r="AO762" s="3"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="3"/>
@@ -32751,6 +33536,7 @@
       <c r="AL763" s="3"/>
       <c r="AM763" s="3"/>
       <c r="AN763" s="3"/>
+      <c r="AO763" s="3"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="3"/>
@@ -32793,6 +33579,7 @@
       <c r="AL764" s="3"/>
       <c r="AM764" s="3"/>
       <c r="AN764" s="3"/>
+      <c r="AO764" s="3"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="3"/>
@@ -32835,6 +33622,7 @@
       <c r="AL765" s="3"/>
       <c r="AM765" s="3"/>
       <c r="AN765" s="3"/>
+      <c r="AO765" s="3"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="3"/>
@@ -32877,6 +33665,7 @@
       <c r="AL766" s="3"/>
       <c r="AM766" s="3"/>
       <c r="AN766" s="3"/>
+      <c r="AO766" s="3"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="3"/>
@@ -32919,6 +33708,7 @@
       <c r="AL767" s="3"/>
       <c r="AM767" s="3"/>
       <c r="AN767" s="3"/>
+      <c r="AO767" s="3"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="3"/>
@@ -32961,6 +33751,7 @@
       <c r="AL768" s="3"/>
       <c r="AM768" s="3"/>
       <c r="AN768" s="3"/>
+      <c r="AO768" s="3"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="3"/>
@@ -33003,6 +33794,7 @@
       <c r="AL769" s="3"/>
       <c r="AM769" s="3"/>
       <c r="AN769" s="3"/>
+      <c r="AO769" s="3"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="3"/>
@@ -33045,6 +33837,7 @@
       <c r="AL770" s="3"/>
       <c r="AM770" s="3"/>
       <c r="AN770" s="3"/>
+      <c r="AO770" s="3"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="3"/>
@@ -33087,6 +33880,7 @@
       <c r="AL771" s="3"/>
       <c r="AM771" s="3"/>
       <c r="AN771" s="3"/>
+      <c r="AO771" s="3"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="3"/>
@@ -33129,6 +33923,7 @@
       <c r="AL772" s="3"/>
       <c r="AM772" s="3"/>
       <c r="AN772" s="3"/>
+      <c r="AO772" s="3"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="3"/>
@@ -33171,6 +33966,7 @@
       <c r="AL773" s="3"/>
       <c r="AM773" s="3"/>
       <c r="AN773" s="3"/>
+      <c r="AO773" s="3"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="3"/>
@@ -33213,6 +34009,7 @@
       <c r="AL774" s="3"/>
       <c r="AM774" s="3"/>
       <c r="AN774" s="3"/>
+      <c r="AO774" s="3"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="3"/>
@@ -33255,6 +34052,7 @@
       <c r="AL775" s="3"/>
       <c r="AM775" s="3"/>
       <c r="AN775" s="3"/>
+      <c r="AO775" s="3"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="3"/>
@@ -33297,6 +34095,7 @@
       <c r="AL776" s="3"/>
       <c r="AM776" s="3"/>
       <c r="AN776" s="3"/>
+      <c r="AO776" s="3"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="3"/>
@@ -33339,6 +34138,7 @@
       <c r="AL777" s="3"/>
       <c r="AM777" s="3"/>
       <c r="AN777" s="3"/>
+      <c r="AO777" s="3"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="3"/>
@@ -33381,6 +34181,7 @@
       <c r="AL778" s="3"/>
       <c r="AM778" s="3"/>
       <c r="AN778" s="3"/>
+      <c r="AO778" s="3"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="3"/>
@@ -33423,6 +34224,7 @@
       <c r="AL779" s="3"/>
       <c r="AM779" s="3"/>
       <c r="AN779" s="3"/>
+      <c r="AO779" s="3"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="3"/>
@@ -33465,6 +34267,7 @@
       <c r="AL780" s="3"/>
       <c r="AM780" s="3"/>
       <c r="AN780" s="3"/>
+      <c r="AO780" s="3"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="3"/>
@@ -33507,6 +34310,7 @@
       <c r="AL781" s="3"/>
       <c r="AM781" s="3"/>
       <c r="AN781" s="3"/>
+      <c r="AO781" s="3"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="3"/>
@@ -33549,6 +34353,7 @@
       <c r="AL782" s="3"/>
       <c r="AM782" s="3"/>
       <c r="AN782" s="3"/>
+      <c r="AO782" s="3"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="3"/>
@@ -33591,6 +34396,7 @@
       <c r="AL783" s="3"/>
       <c r="AM783" s="3"/>
       <c r="AN783" s="3"/>
+      <c r="AO783" s="3"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="3"/>
@@ -33633,6 +34439,7 @@
       <c r="AL784" s="3"/>
       <c r="AM784" s="3"/>
       <c r="AN784" s="3"/>
+      <c r="AO784" s="3"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="3"/>
@@ -33675,6 +34482,7 @@
       <c r="AL785" s="3"/>
       <c r="AM785" s="3"/>
       <c r="AN785" s="3"/>
+      <c r="AO785" s="3"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="3"/>
@@ -33717,6 +34525,7 @@
       <c r="AL786" s="3"/>
       <c r="AM786" s="3"/>
       <c r="AN786" s="3"/>
+      <c r="AO786" s="3"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="3"/>
@@ -33759,6 +34568,7 @@
       <c r="AL787" s="3"/>
       <c r="AM787" s="3"/>
       <c r="AN787" s="3"/>
+      <c r="AO787" s="3"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="3"/>
@@ -33801,6 +34611,7 @@
       <c r="AL788" s="3"/>
       <c r="AM788" s="3"/>
       <c r="AN788" s="3"/>
+      <c r="AO788" s="3"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="3"/>
@@ -33843,6 +34654,7 @@
       <c r="AL789" s="3"/>
       <c r="AM789" s="3"/>
       <c r="AN789" s="3"/>
+      <c r="AO789" s="3"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="3"/>
@@ -33885,6 +34697,7 @@
       <c r="AL790" s="3"/>
       <c r="AM790" s="3"/>
       <c r="AN790" s="3"/>
+      <c r="AO790" s="3"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="3"/>
@@ -33927,6 +34740,7 @@
       <c r="AL791" s="3"/>
       <c r="AM791" s="3"/>
       <c r="AN791" s="3"/>
+      <c r="AO791" s="3"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="3"/>
@@ -33969,6 +34783,7 @@
       <c r="AL792" s="3"/>
       <c r="AM792" s="3"/>
       <c r="AN792" s="3"/>
+      <c r="AO792" s="3"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="3"/>
@@ -34011,6 +34826,7 @@
       <c r="AL793" s="3"/>
       <c r="AM793" s="3"/>
       <c r="AN793" s="3"/>
+      <c r="AO793" s="3"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="3"/>
@@ -34053,6 +34869,7 @@
       <c r="AL794" s="3"/>
       <c r="AM794" s="3"/>
       <c r="AN794" s="3"/>
+      <c r="AO794" s="3"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="3"/>
@@ -34095,6 +34912,7 @@
       <c r="AL795" s="3"/>
       <c r="AM795" s="3"/>
       <c r="AN795" s="3"/>
+      <c r="AO795" s="3"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="3"/>
@@ -34137,6 +34955,7 @@
       <c r="AL796" s="3"/>
       <c r="AM796" s="3"/>
       <c r="AN796" s="3"/>
+      <c r="AO796" s="3"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="3"/>
@@ -34179,6 +34998,7 @@
       <c r="AL797" s="3"/>
       <c r="AM797" s="3"/>
       <c r="AN797" s="3"/>
+      <c r="AO797" s="3"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="3"/>
@@ -34221,6 +35041,7 @@
       <c r="AL798" s="3"/>
       <c r="AM798" s="3"/>
       <c r="AN798" s="3"/>
+      <c r="AO798" s="3"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="3"/>
@@ -34263,6 +35084,7 @@
       <c r="AL799" s="3"/>
       <c r="AM799" s="3"/>
       <c r="AN799" s="3"/>
+      <c r="AO799" s="3"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="3"/>
@@ -34305,6 +35127,7 @@
       <c r="AL800" s="3"/>
       <c r="AM800" s="3"/>
       <c r="AN800" s="3"/>
+      <c r="AO800" s="3"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="3"/>
@@ -34347,6 +35170,7 @@
       <c r="AL801" s="3"/>
       <c r="AM801" s="3"/>
       <c r="AN801" s="3"/>
+      <c r="AO801" s="3"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="3"/>
@@ -34389,6 +35213,7 @@
       <c r="AL802" s="3"/>
       <c r="AM802" s="3"/>
       <c r="AN802" s="3"/>
+      <c r="AO802" s="3"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="3"/>
@@ -34431,6 +35256,7 @@
       <c r="AL803" s="3"/>
       <c r="AM803" s="3"/>
       <c r="AN803" s="3"/>
+      <c r="AO803" s="3"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="3"/>
@@ -34473,6 +35299,7 @@
       <c r="AL804" s="3"/>
       <c r="AM804" s="3"/>
       <c r="AN804" s="3"/>
+      <c r="AO804" s="3"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="3"/>
@@ -34515,6 +35342,7 @@
       <c r="AL805" s="3"/>
       <c r="AM805" s="3"/>
       <c r="AN805" s="3"/>
+      <c r="AO805" s="3"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="3"/>
@@ -34557,6 +35385,7 @@
       <c r="AL806" s="3"/>
       <c r="AM806" s="3"/>
       <c r="AN806" s="3"/>
+      <c r="AO806" s="3"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="3"/>
@@ -34599,6 +35428,7 @@
       <c r="AL807" s="3"/>
       <c r="AM807" s="3"/>
       <c r="AN807" s="3"/>
+      <c r="AO807" s="3"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="3"/>
@@ -34641,6 +35471,7 @@
       <c r="AL808" s="3"/>
       <c r="AM808" s="3"/>
       <c r="AN808" s="3"/>
+      <c r="AO808" s="3"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="3"/>
@@ -34683,6 +35514,7 @@
       <c r="AL809" s="3"/>
       <c r="AM809" s="3"/>
       <c r="AN809" s="3"/>
+      <c r="AO809" s="3"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="3"/>
@@ -34725,6 +35557,7 @@
       <c r="AL810" s="3"/>
       <c r="AM810" s="3"/>
       <c r="AN810" s="3"/>
+      <c r="AO810" s="3"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="3"/>
@@ -34767,6 +35600,7 @@
       <c r="AL811" s="3"/>
       <c r="AM811" s="3"/>
       <c r="AN811" s="3"/>
+      <c r="AO811" s="3"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="3"/>
@@ -34809,6 +35643,7 @@
       <c r="AL812" s="3"/>
       <c r="AM812" s="3"/>
       <c r="AN812" s="3"/>
+      <c r="AO812" s="3"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="3"/>
@@ -34851,6 +35686,7 @@
       <c r="AL813" s="3"/>
       <c r="AM813" s="3"/>
       <c r="AN813" s="3"/>
+      <c r="AO813" s="3"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="3"/>
@@ -34893,6 +35729,7 @@
       <c r="AL814" s="3"/>
       <c r="AM814" s="3"/>
       <c r="AN814" s="3"/>
+      <c r="AO814" s="3"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="3"/>
@@ -34935,6 +35772,7 @@
       <c r="AL815" s="3"/>
       <c r="AM815" s="3"/>
       <c r="AN815" s="3"/>
+      <c r="AO815" s="3"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="3"/>
@@ -34977,6 +35815,7 @@
       <c r="AL816" s="3"/>
       <c r="AM816" s="3"/>
       <c r="AN816" s="3"/>
+      <c r="AO816" s="3"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="3"/>
@@ -35019,6 +35858,7 @@
       <c r="AL817" s="3"/>
       <c r="AM817" s="3"/>
       <c r="AN817" s="3"/>
+      <c r="AO817" s="3"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="3"/>
@@ -35061,6 +35901,7 @@
       <c r="AL818" s="3"/>
       <c r="AM818" s="3"/>
       <c r="AN818" s="3"/>
+      <c r="AO818" s="3"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="3"/>
@@ -35103,6 +35944,7 @@
       <c r="AL819" s="3"/>
       <c r="AM819" s="3"/>
       <c r="AN819" s="3"/>
+      <c r="AO819" s="3"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="3"/>
@@ -35145,6 +35987,7 @@
       <c r="AL820" s="3"/>
       <c r="AM820" s="3"/>
       <c r="AN820" s="3"/>
+      <c r="AO820" s="3"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="3"/>
@@ -35187,6 +36030,7 @@
       <c r="AL821" s="3"/>
       <c r="AM821" s="3"/>
       <c r="AN821" s="3"/>
+      <c r="AO821" s="3"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="3"/>
@@ -35229,6 +36073,7 @@
       <c r="AL822" s="3"/>
       <c r="AM822" s="3"/>
       <c r="AN822" s="3"/>
+      <c r="AO822" s="3"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="3"/>
@@ -35271,6 +36116,7 @@
       <c r="AL823" s="3"/>
       <c r="AM823" s="3"/>
       <c r="AN823" s="3"/>
+      <c r="AO823" s="3"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="3"/>
@@ -35313,6 +36159,7 @@
       <c r="AL824" s="3"/>
       <c r="AM824" s="3"/>
       <c r="AN824" s="3"/>
+      <c r="AO824" s="3"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="3"/>
@@ -35355,6 +36202,7 @@
       <c r="AL825" s="3"/>
       <c r="AM825" s="3"/>
       <c r="AN825" s="3"/>
+      <c r="AO825" s="3"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="3"/>
@@ -35397,6 +36245,7 @@
       <c r="AL826" s="3"/>
       <c r="AM826" s="3"/>
       <c r="AN826" s="3"/>
+      <c r="AO826" s="3"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="3"/>
@@ -35439,6 +36288,7 @@
       <c r="AL827" s="3"/>
       <c r="AM827" s="3"/>
       <c r="AN827" s="3"/>
+      <c r="AO827" s="3"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="3"/>
@@ -35481,6 +36331,7 @@
       <c r="AL828" s="3"/>
       <c r="AM828" s="3"/>
       <c r="AN828" s="3"/>
+      <c r="AO828" s="3"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="3"/>
@@ -35523,6 +36374,7 @@
       <c r="AL829" s="3"/>
       <c r="AM829" s="3"/>
       <c r="AN829" s="3"/>
+      <c r="AO829" s="3"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="3"/>
@@ -35565,6 +36417,7 @@
       <c r="AL830" s="3"/>
       <c r="AM830" s="3"/>
       <c r="AN830" s="3"/>
+      <c r="AO830" s="3"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="3"/>
@@ -35607,6 +36460,7 @@
       <c r="AL831" s="3"/>
       <c r="AM831" s="3"/>
       <c r="AN831" s="3"/>
+      <c r="AO831" s="3"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="3"/>
@@ -35649,6 +36503,7 @@
       <c r="AL832" s="3"/>
       <c r="AM832" s="3"/>
       <c r="AN832" s="3"/>
+      <c r="AO832" s="3"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="3"/>
@@ -35691,6 +36546,7 @@
       <c r="AL833" s="3"/>
       <c r="AM833" s="3"/>
       <c r="AN833" s="3"/>
+      <c r="AO833" s="3"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="3"/>
@@ -35733,6 +36589,7 @@
       <c r="AL834" s="3"/>
       <c r="AM834" s="3"/>
       <c r="AN834" s="3"/>
+      <c r="AO834" s="3"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="3"/>
@@ -35775,6 +36632,7 @@
       <c r="AL835" s="3"/>
       <c r="AM835" s="3"/>
       <c r="AN835" s="3"/>
+      <c r="AO835" s="3"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="3"/>
@@ -35817,6 +36675,7 @@
       <c r="AL836" s="3"/>
       <c r="AM836" s="3"/>
       <c r="AN836" s="3"/>
+      <c r="AO836" s="3"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="3"/>
@@ -35859,6 +36718,7 @@
       <c r="AL837" s="3"/>
       <c r="AM837" s="3"/>
       <c r="AN837" s="3"/>
+      <c r="AO837" s="3"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="3"/>
@@ -35901,6 +36761,7 @@
       <c r="AL838" s="3"/>
       <c r="AM838" s="3"/>
       <c r="AN838" s="3"/>
+      <c r="AO838" s="3"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="3"/>
@@ -35943,6 +36804,7 @@
       <c r="AL839" s="3"/>
       <c r="AM839" s="3"/>
       <c r="AN839" s="3"/>
+      <c r="AO839" s="3"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="3"/>
@@ -35985,6 +36847,7 @@
       <c r="AL840" s="3"/>
       <c r="AM840" s="3"/>
       <c r="AN840" s="3"/>
+      <c r="AO840" s="3"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="3"/>
@@ -36027,6 +36890,7 @@
       <c r="AL841" s="3"/>
       <c r="AM841" s="3"/>
       <c r="AN841" s="3"/>
+      <c r="AO841" s="3"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="3"/>
@@ -36069,6 +36933,7 @@
       <c r="AL842" s="3"/>
       <c r="AM842" s="3"/>
       <c r="AN842" s="3"/>
+      <c r="AO842" s="3"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="3"/>
@@ -36111,6 +36976,7 @@
       <c r="AL843" s="3"/>
       <c r="AM843" s="3"/>
       <c r="AN843" s="3"/>
+      <c r="AO843" s="3"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="3"/>
@@ -36153,6 +37019,7 @@
       <c r="AL844" s="3"/>
       <c r="AM844" s="3"/>
       <c r="AN844" s="3"/>
+      <c r="AO844" s="3"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="3"/>
@@ -36195,6 +37062,7 @@
       <c r="AL845" s="3"/>
       <c r="AM845" s="3"/>
       <c r="AN845" s="3"/>
+      <c r="AO845" s="3"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="3"/>
@@ -36237,6 +37105,7 @@
       <c r="AL846" s="3"/>
       <c r="AM846" s="3"/>
       <c r="AN846" s="3"/>
+      <c r="AO846" s="3"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="3"/>
@@ -36279,6 +37148,7 @@
       <c r="AL847" s="3"/>
       <c r="AM847" s="3"/>
       <c r="AN847" s="3"/>
+      <c r="AO847" s="3"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="3"/>
@@ -36321,6 +37191,7 @@
       <c r="AL848" s="3"/>
       <c r="AM848" s="3"/>
       <c r="AN848" s="3"/>
+      <c r="AO848" s="3"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="3"/>
@@ -36363,6 +37234,7 @@
       <c r="AL849" s="3"/>
       <c r="AM849" s="3"/>
       <c r="AN849" s="3"/>
+      <c r="AO849" s="3"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="3"/>
@@ -36405,6 +37277,7 @@
       <c r="AL850" s="3"/>
       <c r="AM850" s="3"/>
       <c r="AN850" s="3"/>
+      <c r="AO850" s="3"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="3"/>
@@ -36447,6 +37320,7 @@
       <c r="AL851" s="3"/>
       <c r="AM851" s="3"/>
       <c r="AN851" s="3"/>
+      <c r="AO851" s="3"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="3"/>
@@ -36489,6 +37363,7 @@
       <c r="AL852" s="3"/>
       <c r="AM852" s="3"/>
       <c r="AN852" s="3"/>
+      <c r="AO852" s="3"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="3"/>
@@ -36531,6 +37406,7 @@
       <c r="AL853" s="3"/>
       <c r="AM853" s="3"/>
       <c r="AN853" s="3"/>
+      <c r="AO853" s="3"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="3"/>
@@ -36573,6 +37449,7 @@
       <c r="AL854" s="3"/>
       <c r="AM854" s="3"/>
       <c r="AN854" s="3"/>
+      <c r="AO854" s="3"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="3"/>
@@ -36615,6 +37492,7 @@
       <c r="AL855" s="3"/>
       <c r="AM855" s="3"/>
       <c r="AN855" s="3"/>
+      <c r="AO855" s="3"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="3"/>
@@ -36657,6 +37535,7 @@
       <c r="AL856" s="3"/>
       <c r="AM856" s="3"/>
       <c r="AN856" s="3"/>
+      <c r="AO856" s="3"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="3"/>
@@ -36699,6 +37578,7 @@
       <c r="AL857" s="3"/>
       <c r="AM857" s="3"/>
       <c r="AN857" s="3"/>
+      <c r="AO857" s="3"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="3"/>
@@ -36741,6 +37621,7 @@
       <c r="AL858" s="3"/>
       <c r="AM858" s="3"/>
       <c r="AN858" s="3"/>
+      <c r="AO858" s="3"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="3"/>
@@ -36783,6 +37664,7 @@
       <c r="AL859" s="3"/>
       <c r="AM859" s="3"/>
       <c r="AN859" s="3"/>
+      <c r="AO859" s="3"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="3"/>
@@ -36825,6 +37707,7 @@
       <c r="AL860" s="3"/>
       <c r="AM860" s="3"/>
       <c r="AN860" s="3"/>
+      <c r="AO860" s="3"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="3"/>
@@ -36867,6 +37750,7 @@
       <c r="AL861" s="3"/>
       <c r="AM861" s="3"/>
       <c r="AN861" s="3"/>
+      <c r="AO861" s="3"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="3"/>
@@ -36909,6 +37793,7 @@
       <c r="AL862" s="3"/>
       <c r="AM862" s="3"/>
       <c r="AN862" s="3"/>
+      <c r="AO862" s="3"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="3"/>
@@ -36951,6 +37836,7 @@
       <c r="AL863" s="3"/>
       <c r="AM863" s="3"/>
       <c r="AN863" s="3"/>
+      <c r="AO863" s="3"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="3"/>
@@ -36993,6 +37879,7 @@
       <c r="AL864" s="3"/>
       <c r="AM864" s="3"/>
       <c r="AN864" s="3"/>
+      <c r="AO864" s="3"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
       <c r="A865" s="3"/>
@@ -37035,6 +37922,7 @@
       <c r="AL865" s="3"/>
       <c r="AM865" s="3"/>
       <c r="AN865" s="3"/>
+      <c r="AO865" s="3"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="3"/>
@@ -37077,6 +37965,7 @@
       <c r="AL866" s="3"/>
       <c r="AM866" s="3"/>
       <c r="AN866" s="3"/>
+      <c r="AO866" s="3"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="3"/>
@@ -37119,6 +38008,7 @@
       <c r="AL867" s="3"/>
       <c r="AM867" s="3"/>
       <c r="AN867" s="3"/>
+      <c r="AO867" s="3"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="3"/>
@@ -37161,6 +38051,7 @@
       <c r="AL868" s="3"/>
       <c r="AM868" s="3"/>
       <c r="AN868" s="3"/>
+      <c r="AO868" s="3"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="3"/>
@@ -37203,6 +38094,7 @@
       <c r="AL869" s="3"/>
       <c r="AM869" s="3"/>
       <c r="AN869" s="3"/>
+      <c r="AO869" s="3"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="3"/>
@@ -37245,6 +38137,7 @@
       <c r="AL870" s="3"/>
       <c r="AM870" s="3"/>
       <c r="AN870" s="3"/>
+      <c r="AO870" s="3"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="3"/>
@@ -37287,6 +38180,7 @@
       <c r="AL871" s="3"/>
       <c r="AM871" s="3"/>
       <c r="AN871" s="3"/>
+      <c r="AO871" s="3"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="3"/>
@@ -37329,6 +38223,7 @@
       <c r="AL872" s="3"/>
       <c r="AM872" s="3"/>
       <c r="AN872" s="3"/>
+      <c r="AO872" s="3"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="3"/>
@@ -37371,6 +38266,7 @@
       <c r="AL873" s="3"/>
       <c r="AM873" s="3"/>
       <c r="AN873" s="3"/>
+      <c r="AO873" s="3"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="3"/>
@@ -37413,6 +38309,7 @@
       <c r="AL874" s="3"/>
       <c r="AM874" s="3"/>
       <c r="AN874" s="3"/>
+      <c r="AO874" s="3"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="3"/>
@@ -37455,6 +38352,7 @@
       <c r="AL875" s="3"/>
       <c r="AM875" s="3"/>
       <c r="AN875" s="3"/>
+      <c r="AO875" s="3"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="3"/>
@@ -37497,6 +38395,7 @@
       <c r="AL876" s="3"/>
       <c r="AM876" s="3"/>
       <c r="AN876" s="3"/>
+      <c r="AO876" s="3"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="3"/>
@@ -37539,6 +38438,7 @@
       <c r="AL877" s="3"/>
       <c r="AM877" s="3"/>
       <c r="AN877" s="3"/>
+      <c r="AO877" s="3"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="3"/>
@@ -37581,6 +38481,7 @@
       <c r="AL878" s="3"/>
       <c r="AM878" s="3"/>
       <c r="AN878" s="3"/>
+      <c r="AO878" s="3"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="3"/>
@@ -37623,6 +38524,7 @@
       <c r="AL879" s="3"/>
       <c r="AM879" s="3"/>
       <c r="AN879" s="3"/>
+      <c r="AO879" s="3"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="3"/>
@@ -37665,6 +38567,7 @@
       <c r="AL880" s="3"/>
       <c r="AM880" s="3"/>
       <c r="AN880" s="3"/>
+      <c r="AO880" s="3"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="3"/>
@@ -37707,6 +38610,7 @@
       <c r="AL881" s="3"/>
       <c r="AM881" s="3"/>
       <c r="AN881" s="3"/>
+      <c r="AO881" s="3"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="3"/>
@@ -37749,6 +38653,7 @@
       <c r="AL882" s="3"/>
       <c r="AM882" s="3"/>
       <c r="AN882" s="3"/>
+      <c r="AO882" s="3"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="3"/>
@@ -37791,6 +38696,7 @@
       <c r="AL883" s="3"/>
       <c r="AM883" s="3"/>
       <c r="AN883" s="3"/>
+      <c r="AO883" s="3"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="3"/>
@@ -37833,6 +38739,7 @@
       <c r="AL884" s="3"/>
       <c r="AM884" s="3"/>
       <c r="AN884" s="3"/>
+      <c r="AO884" s="3"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="3"/>
@@ -37875,6 +38782,7 @@
       <c r="AL885" s="3"/>
       <c r="AM885" s="3"/>
       <c r="AN885" s="3"/>
+      <c r="AO885" s="3"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="3"/>
@@ -37917,6 +38825,7 @@
       <c r="AL886" s="3"/>
       <c r="AM886" s="3"/>
       <c r="AN886" s="3"/>
+      <c r="AO886" s="3"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="3"/>
@@ -37959,6 +38868,7 @@
       <c r="AL887" s="3"/>
       <c r="AM887" s="3"/>
       <c r="AN887" s="3"/>
+      <c r="AO887" s="3"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="3"/>
@@ -38001,6 +38911,7 @@
       <c r="AL888" s="3"/>
       <c r="AM888" s="3"/>
       <c r="AN888" s="3"/>
+      <c r="AO888" s="3"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="3"/>
@@ -38043,6 +38954,7 @@
       <c r="AL889" s="3"/>
       <c r="AM889" s="3"/>
       <c r="AN889" s="3"/>
+      <c r="AO889" s="3"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="3"/>
@@ -38085,6 +38997,7 @@
       <c r="AL890" s="3"/>
       <c r="AM890" s="3"/>
       <c r="AN890" s="3"/>
+      <c r="AO890" s="3"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="3"/>
@@ -38127,6 +39040,7 @@
       <c r="AL891" s="3"/>
       <c r="AM891" s="3"/>
       <c r="AN891" s="3"/>
+      <c r="AO891" s="3"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="3"/>
@@ -38169,6 +39083,7 @@
       <c r="AL892" s="3"/>
       <c r="AM892" s="3"/>
       <c r="AN892" s="3"/>
+      <c r="AO892" s="3"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="3"/>
@@ -38211,6 +39126,7 @@
       <c r="AL893" s="3"/>
       <c r="AM893" s="3"/>
       <c r="AN893" s="3"/>
+      <c r="AO893" s="3"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="3"/>
@@ -38253,6 +39169,7 @@
       <c r="AL894" s="3"/>
       <c r="AM894" s="3"/>
       <c r="AN894" s="3"/>
+      <c r="AO894" s="3"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="3"/>
@@ -38295,6 +39212,7 @@
       <c r="AL895" s="3"/>
       <c r="AM895" s="3"/>
       <c r="AN895" s="3"/>
+      <c r="AO895" s="3"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="3"/>
@@ -38337,6 +39255,7 @@
       <c r="AL896" s="3"/>
       <c r="AM896" s="3"/>
       <c r="AN896" s="3"/>
+      <c r="AO896" s="3"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="3"/>
@@ -38379,6 +39298,7 @@
       <c r="AL897" s="3"/>
       <c r="AM897" s="3"/>
       <c r="AN897" s="3"/>
+      <c r="AO897" s="3"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="3"/>
@@ -38421,6 +39341,7 @@
       <c r="AL898" s="3"/>
       <c r="AM898" s="3"/>
       <c r="AN898" s="3"/>
+      <c r="AO898" s="3"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="3"/>
@@ -38463,6 +39384,7 @@
       <c r="AL899" s="3"/>
       <c r="AM899" s="3"/>
       <c r="AN899" s="3"/>
+      <c r="AO899" s="3"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="3"/>
@@ -38505,6 +39427,7 @@
       <c r="AL900" s="3"/>
       <c r="AM900" s="3"/>
       <c r="AN900" s="3"/>
+      <c r="AO900" s="3"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="3"/>
@@ -38547,6 +39470,7 @@
       <c r="AL901" s="3"/>
       <c r="AM901" s="3"/>
       <c r="AN901" s="3"/>
+      <c r="AO901" s="3"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="3"/>
@@ -38589,6 +39513,7 @@
       <c r="AL902" s="3"/>
       <c r="AM902" s="3"/>
       <c r="AN902" s="3"/>
+      <c r="AO902" s="3"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="3"/>
@@ -38631,6 +39556,7 @@
       <c r="AL903" s="3"/>
       <c r="AM903" s="3"/>
       <c r="AN903" s="3"/>
+      <c r="AO903" s="3"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="3"/>
@@ -38673,6 +39599,7 @@
       <c r="AL904" s="3"/>
       <c r="AM904" s="3"/>
       <c r="AN904" s="3"/>
+      <c r="AO904" s="3"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="3"/>
@@ -38715,6 +39642,7 @@
       <c r="AL905" s="3"/>
       <c r="AM905" s="3"/>
       <c r="AN905" s="3"/>
+      <c r="AO905" s="3"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="3"/>
@@ -38757,6 +39685,7 @@
       <c r="AL906" s="3"/>
       <c r="AM906" s="3"/>
       <c r="AN906" s="3"/>
+      <c r="AO906" s="3"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="3"/>
@@ -38799,6 +39728,7 @@
       <c r="AL907" s="3"/>
       <c r="AM907" s="3"/>
       <c r="AN907" s="3"/>
+      <c r="AO907" s="3"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="3"/>
@@ -38841,6 +39771,7 @@
       <c r="AL908" s="3"/>
       <c r="AM908" s="3"/>
       <c r="AN908" s="3"/>
+      <c r="AO908" s="3"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="3"/>
@@ -38883,6 +39814,7 @@
       <c r="AL909" s="3"/>
       <c r="AM909" s="3"/>
       <c r="AN909" s="3"/>
+      <c r="AO909" s="3"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="3"/>
@@ -38925,6 +39857,7 @@
       <c r="AL910" s="3"/>
       <c r="AM910" s="3"/>
       <c r="AN910" s="3"/>
+      <c r="AO910" s="3"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="3"/>
@@ -38967,6 +39900,7 @@
       <c r="AL911" s="3"/>
       <c r="AM911" s="3"/>
       <c r="AN911" s="3"/>
+      <c r="AO911" s="3"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="3"/>
@@ -39009,6 +39943,7 @@
       <c r="AL912" s="3"/>
       <c r="AM912" s="3"/>
       <c r="AN912" s="3"/>
+      <c r="AO912" s="3"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="3"/>
@@ -39051,6 +39986,7 @@
       <c r="AL913" s="3"/>
       <c r="AM913" s="3"/>
       <c r="AN913" s="3"/>
+      <c r="AO913" s="3"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="3"/>
@@ -39093,6 +40029,7 @@
       <c r="AL914" s="3"/>
       <c r="AM914" s="3"/>
       <c r="AN914" s="3"/>
+      <c r="AO914" s="3"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="3"/>
@@ -39135,6 +40072,7 @@
       <c r="AL915" s="3"/>
       <c r="AM915" s="3"/>
       <c r="AN915" s="3"/>
+      <c r="AO915" s="3"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="3"/>
@@ -39177,6 +40115,7 @@
       <c r="AL916" s="3"/>
       <c r="AM916" s="3"/>
       <c r="AN916" s="3"/>
+      <c r="AO916" s="3"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="3"/>
@@ -39219,6 +40158,7 @@
       <c r="AL917" s="3"/>
       <c r="AM917" s="3"/>
       <c r="AN917" s="3"/>
+      <c r="AO917" s="3"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="3"/>
@@ -39261,6 +40201,7 @@
       <c r="AL918" s="3"/>
       <c r="AM918" s="3"/>
       <c r="AN918" s="3"/>
+      <c r="AO918" s="3"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
       <c r="A919" s="3"/>
@@ -39303,6 +40244,7 @@
       <c r="AL919" s="3"/>
       <c r="AM919" s="3"/>
       <c r="AN919" s="3"/>
+      <c r="AO919" s="3"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="3"/>
@@ -39345,6 +40287,7 @@
       <c r="AL920" s="3"/>
       <c r="AM920" s="3"/>
       <c r="AN920" s="3"/>
+      <c r="AO920" s="3"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="3"/>
@@ -39387,6 +40330,7 @@
       <c r="AL921" s="3"/>
       <c r="AM921" s="3"/>
       <c r="AN921" s="3"/>
+      <c r="AO921" s="3"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="3"/>
@@ -39429,6 +40373,7 @@
       <c r="AL922" s="3"/>
       <c r="AM922" s="3"/>
       <c r="AN922" s="3"/>
+      <c r="AO922" s="3"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="3"/>
@@ -39471,6 +40416,7 @@
       <c r="AL923" s="3"/>
       <c r="AM923" s="3"/>
       <c r="AN923" s="3"/>
+      <c r="AO923" s="3"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="3"/>
@@ -39513,6 +40459,7 @@
       <c r="AL924" s="3"/>
       <c r="AM924" s="3"/>
       <c r="AN924" s="3"/>
+      <c r="AO924" s="3"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="3"/>
@@ -39555,6 +40502,7 @@
       <c r="AL925" s="3"/>
       <c r="AM925" s="3"/>
       <c r="AN925" s="3"/>
+      <c r="AO925" s="3"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="3"/>
@@ -39597,6 +40545,7 @@
       <c r="AL926" s="3"/>
       <c r="AM926" s="3"/>
       <c r="AN926" s="3"/>
+      <c r="AO926" s="3"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="3"/>
@@ -39639,6 +40588,7 @@
       <c r="AL927" s="3"/>
       <c r="AM927" s="3"/>
       <c r="AN927" s="3"/>
+      <c r="AO927" s="3"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
       <c r="A928" s="3"/>
@@ -39681,6 +40631,7 @@
       <c r="AL928" s="3"/>
       <c r="AM928" s="3"/>
       <c r="AN928" s="3"/>
+      <c r="AO928" s="3"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="3"/>
@@ -39723,6 +40674,7 @@
       <c r="AL929" s="3"/>
       <c r="AM929" s="3"/>
       <c r="AN929" s="3"/>
+      <c r="AO929" s="3"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="3"/>
@@ -39765,6 +40717,7 @@
       <c r="AL930" s="3"/>
       <c r="AM930" s="3"/>
       <c r="AN930" s="3"/>
+      <c r="AO930" s="3"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="3"/>
@@ -39807,6 +40760,7 @@
       <c r="AL931" s="3"/>
       <c r="AM931" s="3"/>
       <c r="AN931" s="3"/>
+      <c r="AO931" s="3"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="3"/>
@@ -39849,6 +40803,7 @@
       <c r="AL932" s="3"/>
       <c r="AM932" s="3"/>
       <c r="AN932" s="3"/>
+      <c r="AO932" s="3"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="3"/>
@@ -39891,6 +40846,7 @@
       <c r="AL933" s="3"/>
       <c r="AM933" s="3"/>
       <c r="AN933" s="3"/>
+      <c r="AO933" s="3"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="3"/>
@@ -39933,6 +40889,7 @@
       <c r="AL934" s="3"/>
       <c r="AM934" s="3"/>
       <c r="AN934" s="3"/>
+      <c r="AO934" s="3"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="3"/>
@@ -39975,6 +40932,7 @@
       <c r="AL935" s="3"/>
       <c r="AM935" s="3"/>
       <c r="AN935" s="3"/>
+      <c r="AO935" s="3"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="3"/>
@@ -40017,6 +40975,7 @@
       <c r="AL936" s="3"/>
       <c r="AM936" s="3"/>
       <c r="AN936" s="3"/>
+      <c r="AO936" s="3"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
       <c r="A937" s="3"/>
@@ -40059,6 +41018,7 @@
       <c r="AL937" s="3"/>
       <c r="AM937" s="3"/>
       <c r="AN937" s="3"/>
+      <c r="AO937" s="3"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="3"/>
@@ -40101,6 +41061,7 @@
       <c r="AL938" s="3"/>
       <c r="AM938" s="3"/>
       <c r="AN938" s="3"/>
+      <c r="AO938" s="3"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="3"/>
@@ -40143,6 +41104,7 @@
       <c r="AL939" s="3"/>
       <c r="AM939" s="3"/>
       <c r="AN939" s="3"/>
+      <c r="AO939" s="3"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="3"/>
@@ -40185,6 +41147,7 @@
       <c r="AL940" s="3"/>
       <c r="AM940" s="3"/>
       <c r="AN940" s="3"/>
+      <c r="AO940" s="3"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
       <c r="A941" s="3"/>
@@ -40227,6 +41190,7 @@
       <c r="AL941" s="3"/>
       <c r="AM941" s="3"/>
       <c r="AN941" s="3"/>
+      <c r="AO941" s="3"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
       <c r="A942" s="3"/>
@@ -40269,6 +41233,7 @@
       <c r="AL942" s="3"/>
       <c r="AM942" s="3"/>
       <c r="AN942" s="3"/>
+      <c r="AO942" s="3"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
       <c r="A943" s="3"/>
@@ -40311,6 +41276,7 @@
       <c r="AL943" s="3"/>
       <c r="AM943" s="3"/>
       <c r="AN943" s="3"/>
+      <c r="AO943" s="3"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
       <c r="A944" s="3"/>
@@ -40353,6 +41319,7 @@
       <c r="AL944" s="3"/>
       <c r="AM944" s="3"/>
       <c r="AN944" s="3"/>
+      <c r="AO944" s="3"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
       <c r="A945" s="3"/>
@@ -40395,6 +41362,7 @@
       <c r="AL945" s="3"/>
       <c r="AM945" s="3"/>
       <c r="AN945" s="3"/>
+      <c r="AO945" s="3"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
       <c r="A946" s="3"/>
@@ -40437,6 +41405,7 @@
       <c r="AL946" s="3"/>
       <c r="AM946" s="3"/>
       <c r="AN946" s="3"/>
+      <c r="AO946" s="3"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
       <c r="A947" s="3"/>
@@ -40479,6 +41448,7 @@
       <c r="AL947" s="3"/>
       <c r="AM947" s="3"/>
       <c r="AN947" s="3"/>
+      <c r="AO947" s="3"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
       <c r="A948" s="3"/>
@@ -40521,6 +41491,7 @@
       <c r="AL948" s="3"/>
       <c r="AM948" s="3"/>
       <c r="AN948" s="3"/>
+      <c r="AO948" s="3"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
       <c r="A949" s="3"/>
@@ -40563,6 +41534,7 @@
       <c r="AL949" s="3"/>
       <c r="AM949" s="3"/>
       <c r="AN949" s="3"/>
+      <c r="AO949" s="3"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
       <c r="A950" s="3"/>
@@ -40605,6 +41577,7 @@
       <c r="AL950" s="3"/>
       <c r="AM950" s="3"/>
       <c r="AN950" s="3"/>
+      <c r="AO950" s="3"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
       <c r="A951" s="3"/>
@@ -40647,6 +41620,7 @@
       <c r="AL951" s="3"/>
       <c r="AM951" s="3"/>
       <c r="AN951" s="3"/>
+      <c r="AO951" s="3"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
       <c r="A952" s="3"/>
@@ -40689,6 +41663,7 @@
       <c r="AL952" s="3"/>
       <c r="AM952" s="3"/>
       <c r="AN952" s="3"/>
+      <c r="AO952" s="3"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
       <c r="A953" s="3"/>
@@ -40731,6 +41706,7 @@
       <c r="AL953" s="3"/>
       <c r="AM953" s="3"/>
       <c r="AN953" s="3"/>
+      <c r="AO953" s="3"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
       <c r="A954" s="3"/>
@@ -40773,6 +41749,7 @@
       <c r="AL954" s="3"/>
       <c r="AM954" s="3"/>
       <c r="AN954" s="3"/>
+      <c r="AO954" s="3"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
       <c r="A955" s="3"/>
@@ -40815,6 +41792,7 @@
       <c r="AL955" s="3"/>
       <c r="AM955" s="3"/>
       <c r="AN955" s="3"/>
+      <c r="AO955" s="3"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
       <c r="A956" s="3"/>
@@ -40857,6 +41835,7 @@
       <c r="AL956" s="3"/>
       <c r="AM956" s="3"/>
       <c r="AN956" s="3"/>
+      <c r="AO956" s="3"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
       <c r="A957" s="3"/>
@@ -40899,6 +41878,7 @@
       <c r="AL957" s="3"/>
       <c r="AM957" s="3"/>
       <c r="AN957" s="3"/>
+      <c r="AO957" s="3"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
       <c r="A958" s="3"/>
@@ -40941,6 +41921,7 @@
       <c r="AL958" s="3"/>
       <c r="AM958" s="3"/>
       <c r="AN958" s="3"/>
+      <c r="AO958" s="3"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
       <c r="A959" s="3"/>
@@ -40983,6 +41964,7 @@
       <c r="AL959" s="3"/>
       <c r="AM959" s="3"/>
       <c r="AN959" s="3"/>
+      <c r="AO959" s="3"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
       <c r="A960" s="3"/>
@@ -41025,6 +42007,7 @@
       <c r="AL960" s="3"/>
       <c r="AM960" s="3"/>
       <c r="AN960" s="3"/>
+      <c r="AO960" s="3"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
       <c r="A961" s="3"/>
@@ -41067,6 +42050,7 @@
       <c r="AL961" s="3"/>
       <c r="AM961" s="3"/>
       <c r="AN961" s="3"/>
+      <c r="AO961" s="3"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
       <c r="A962" s="3"/>
@@ -41109,6 +42093,7 @@
       <c r="AL962" s="3"/>
       <c r="AM962" s="3"/>
       <c r="AN962" s="3"/>
+      <c r="AO962" s="3"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
       <c r="A963" s="3"/>
@@ -41151,6 +42136,7 @@
       <c r="AL963" s="3"/>
       <c r="AM963" s="3"/>
       <c r="AN963" s="3"/>
+      <c r="AO963" s="3"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
       <c r="A964" s="3"/>
@@ -41193,6 +42179,7 @@
       <c r="AL964" s="3"/>
       <c r="AM964" s="3"/>
       <c r="AN964" s="3"/>
+      <c r="AO964" s="3"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
       <c r="A965" s="3"/>
@@ -41235,6 +42222,7 @@
       <c r="AL965" s="3"/>
       <c r="AM965" s="3"/>
       <c r="AN965" s="3"/>
+      <c r="AO965" s="3"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
       <c r="A966" s="3"/>
@@ -41277,6 +42265,7 @@
       <c r="AL966" s="3"/>
       <c r="AM966" s="3"/>
       <c r="AN966" s="3"/>
+      <c r="AO966" s="3"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
       <c r="A967" s="3"/>
@@ -41319,6 +42308,7 @@
       <c r="AL967" s="3"/>
       <c r="AM967" s="3"/>
       <c r="AN967" s="3"/>
+      <c r="AO967" s="3"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
       <c r="A968" s="3"/>
@@ -41361,6 +42351,7 @@
       <c r="AL968" s="3"/>
       <c r="AM968" s="3"/>
       <c r="AN968" s="3"/>
+      <c r="AO968" s="3"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
       <c r="A969" s="3"/>
@@ -41403,6 +42394,7 @@
       <c r="AL969" s="3"/>
       <c r="AM969" s="3"/>
       <c r="AN969" s="3"/>
+      <c r="AO969" s="3"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
       <c r="A970" s="3"/>
@@ -41445,6 +42437,7 @@
       <c r="AL970" s="3"/>
       <c r="AM970" s="3"/>
       <c r="AN970" s="3"/>
+      <c r="AO970" s="3"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
       <c r="A971" s="3"/>
@@ -41487,6 +42480,7 @@
       <c r="AL971" s="3"/>
       <c r="AM971" s="3"/>
       <c r="AN971" s="3"/>
+      <c r="AO971" s="3"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
       <c r="A972" s="3"/>
@@ -41529,6 +42523,7 @@
       <c r="AL972" s="3"/>
       <c r="AM972" s="3"/>
       <c r="AN972" s="3"/>
+      <c r="AO972" s="3"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
       <c r="A973" s="3"/>
@@ -41571,6 +42566,7 @@
       <c r="AL973" s="3"/>
       <c r="AM973" s="3"/>
       <c r="AN973" s="3"/>
+      <c r="AO973" s="3"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
       <c r="A974" s="3"/>
@@ -41613,6 +42609,7 @@
       <c r="AL974" s="3"/>
       <c r="AM974" s="3"/>
       <c r="AN974" s="3"/>
+      <c r="AO974" s="3"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
       <c r="A975" s="3"/>
@@ -41655,6 +42652,7 @@
       <c r="AL975" s="3"/>
       <c r="AM975" s="3"/>
       <c r="AN975" s="3"/>
+      <c r="AO975" s="3"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
       <c r="A976" s="3"/>
@@ -41697,6 +42695,7 @@
       <c r="AL976" s="3"/>
       <c r="AM976" s="3"/>
       <c r="AN976" s="3"/>
+      <c r="AO976" s="3"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
       <c r="A977" s="3"/>
@@ -41739,6 +42738,7 @@
       <c r="AL977" s="3"/>
       <c r="AM977" s="3"/>
       <c r="AN977" s="3"/>
+      <c r="AO977" s="3"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
       <c r="A978" s="3"/>
@@ -41781,6 +42781,7 @@
       <c r="AL978" s="3"/>
       <c r="AM978" s="3"/>
       <c r="AN978" s="3"/>
+      <c r="AO978" s="3"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
       <c r="A979" s="3"/>
@@ -41823,6 +42824,7 @@
       <c r="AL979" s="3"/>
       <c r="AM979" s="3"/>
       <c r="AN979" s="3"/>
+      <c r="AO979" s="3"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
       <c r="A980" s="3"/>
@@ -41865,6 +42867,7 @@
       <c r="AL980" s="3"/>
       <c r="AM980" s="3"/>
       <c r="AN980" s="3"/>
+      <c r="AO980" s="3"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
       <c r="A981" s="3"/>
@@ -41907,6 +42910,7 @@
       <c r="AL981" s="3"/>
       <c r="AM981" s="3"/>
       <c r="AN981" s="3"/>
+      <c r="AO981" s="3"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
       <c r="A982" s="3"/>
@@ -41949,6 +42953,7 @@
       <c r="AL982" s="3"/>
       <c r="AM982" s="3"/>
       <c r="AN982" s="3"/>
+      <c r="AO982" s="3"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
       <c r="A983" s="3"/>
@@ -41991,6 +42996,7 @@
       <c r="AL983" s="3"/>
       <c r="AM983" s="3"/>
       <c r="AN983" s="3"/>
+      <c r="AO983" s="3"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
       <c r="A984" s="3"/>
@@ -42033,6 +43039,7 @@
       <c r="AL984" s="3"/>
       <c r="AM984" s="3"/>
       <c r="AN984" s="3"/>
+      <c r="AO984" s="3"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
       <c r="A985" s="3"/>
@@ -42075,6 +43082,7 @@
       <c r="AL985" s="3"/>
       <c r="AM985" s="3"/>
       <c r="AN985" s="3"/>
+      <c r="AO985" s="3"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
       <c r="A986" s="3"/>
@@ -42117,6 +43125,7 @@
       <c r="AL986" s="3"/>
       <c r="AM986" s="3"/>
       <c r="AN986" s="3"/>
+      <c r="AO986" s="3"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
       <c r="A987" s="3"/>
@@ -42159,6 +43168,7 @@
       <c r="AL987" s="3"/>
       <c r="AM987" s="3"/>
       <c r="AN987" s="3"/>
+      <c r="AO987" s="3"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
       <c r="A988" s="3"/>
@@ -42201,6 +43211,7 @@
       <c r="AL988" s="3"/>
       <c r="AM988" s="3"/>
       <c r="AN988" s="3"/>
+      <c r="AO988" s="3"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
       <c r="A989" s="3"/>
@@ -42243,6 +43254,7 @@
       <c r="AL989" s="3"/>
       <c r="AM989" s="3"/>
       <c r="AN989" s="3"/>
+      <c r="AO989" s="3"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
       <c r="A990" s="3"/>
@@ -42285,6 +43297,7 @@
       <c r="AL990" s="3"/>
       <c r="AM990" s="3"/>
       <c r="AN990" s="3"/>
+      <c r="AO990" s="3"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
       <c r="A991" s="3"/>
@@ -42327,6 +43340,7 @@
       <c r="AL991" s="3"/>
       <c r="AM991" s="3"/>
       <c r="AN991" s="3"/>
+      <c r="AO991" s="3"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
       <c r="A992" s="3"/>
@@ -42369,6 +43383,7 @@
       <c r="AL992" s="3"/>
       <c r="AM992" s="3"/>
       <c r="AN992" s="3"/>
+      <c r="AO992" s="3"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
       <c r="A993" s="3"/>
@@ -42411,6 +43426,7 @@
       <c r="AL993" s="3"/>
       <c r="AM993" s="3"/>
       <c r="AN993" s="3"/>
+      <c r="AO993" s="3"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
       <c r="A994" s="3"/>
@@ -42453,6 +43469,7 @@
       <c r="AL994" s="3"/>
       <c r="AM994" s="3"/>
       <c r="AN994" s="3"/>
+      <c r="AO994" s="3"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
       <c r="A995" s="3"/>
@@ -42495,6 +43512,7 @@
       <c r="AL995" s="3"/>
       <c r="AM995" s="3"/>
       <c r="AN995" s="3"/>
+      <c r="AO995" s="3"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
       <c r="A996" s="3"/>
@@ -42537,6 +43555,7 @@
       <c r="AL996" s="3"/>
       <c r="AM996" s="3"/>
       <c r="AN996" s="3"/>
+      <c r="AO996" s="3"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
       <c r="A997" s="3"/>
@@ -42579,6 +43598,7 @@
       <c r="AL997" s="3"/>
       <c r="AM997" s="3"/>
       <c r="AN997" s="3"/>
+      <c r="AO997" s="3"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
       <c r="A998" s="3"/>
@@ -42621,6 +43641,7 @@
       <c r="AL998" s="3"/>
       <c r="AM998" s="3"/>
       <c r="AN998" s="3"/>
+      <c r="AO998" s="3"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
       <c r="A999" s="3"/>
@@ -42663,6 +43684,7 @@
       <c r="AL999" s="3"/>
       <c r="AM999" s="3"/>
       <c r="AN999" s="3"/>
+      <c r="AO999" s="3"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
       <c r="A1000" s="3"/>
@@ -42705,11 +43727,12 @@
       <c r="AL1000" s="3"/>
       <c r="AM1000" s="3"/>
       <c r="AN1000" s="3"/>
+      <c r="AO1000" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="Q2"/>
-    <hyperlink r:id="rId2" ref="AK2"/>
+    <hyperlink r:id="rId1" ref="R2"/>
+    <hyperlink r:id="rId2" ref="AL2"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
